--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B07C84CE-2C88-4C58-AD22-CC8F8BB5F1FB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -478,7 +478,7 @@
       <name val="Helvetica"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,13 +490,43 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="24">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -538,8 +568,229 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -551,42 +802,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -598,19 +843,97 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -619,6 +942,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF66"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4572,1296 +4900,1302 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="42" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="34"/>
+      <c r="G4" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="35"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="36"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4" t="s">
+      <c r="A6" s="36"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
+      <c r="H6" s="37"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="38"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="40"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4" t="s">
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5" t="s">
+      <c r="H8" s="35"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="40"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="34"/>
+      <c r="C10" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5" t="s">
+      <c r="A11" s="36"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="37"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="4" t="s">
+      <c r="A12" s="36"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
+      <c r="H12" s="37"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="38"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="H13" s="40"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="34"/>
+      <c r="C15" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4" t="s">
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5" t="s">
+      <c r="G15" s="34"/>
+      <c r="H15" s="35"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="4" t="s">
+      <c r="G17" s="34"/>
+      <c r="H17" s="35" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="36"/>
+      <c r="B18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="s">
+      <c r="G18" s="4"/>
+      <c r="H18" s="37" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="4" t="s">
+      <c r="A19" s="36"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="37"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5" t="s">
+      <c r="A20" s="36"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="37"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="4" t="s">
+      <c r="A21" s="36"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5" t="s">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="37"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="4" t="s">
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5" t="s">
+      <c r="H23" s="35"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="40"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="4" t="s">
+      <c r="C25" s="34"/>
+      <c r="D25" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="4" t="s">
+      <c r="E25" s="34"/>
+      <c r="F25" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="36"/>
+      <c r="B26" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5" t="s">
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="37" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="4" t="s">
+      <c r="A27" s="36"/>
+      <c r="B27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="4" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="4" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="41" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="5" t="s">
+      <c r="A28" s="36"/>
+      <c r="B28" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="37" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="4" t="s">
+      <c r="A29" s="36"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="4" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="37"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5" t="s">
+      <c r="A30" s="36"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H30" s="5"/>
+      <c r="H30" s="37"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="4" t="s">
+      <c r="A31" s="36"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="37"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5" t="s">
+      <c r="A32" s="36"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="37"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="4" t="s">
+      <c r="A33" s="36"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="37"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5" t="s">
+      <c r="A34" s="36"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="37"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="4" t="s">
+      <c r="A35" s="36"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5" t="s">
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="37"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="38"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="40"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5" t="s">
+      <c r="A38" s="15"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="4" t="s">
+      <c r="C39" s="4"/>
+      <c r="D39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="15"/>
+      <c r="B40" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5" t="s">
+      <c r="C40" s="4"/>
+      <c r="D40" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="4" t="s">
+      <c r="A41" s="15"/>
+      <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="4" t="s">
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="5" t="s">
+      <c r="A42" s="15"/>
+      <c r="B42" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5" t="s">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="4" t="s">
+      <c r="A43" s="15"/>
+      <c r="B43" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="5" t="s">
+      <c r="A44" s="15"/>
+      <c r="B44" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="4" t="s">
+      <c r="A45" s="15"/>
+      <c r="B45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="5" t="s">
+      <c r="A46" s="15"/>
+      <c r="B46" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="4" t="s">
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="4" t="s">
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H47" s="5"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5" t="s">
+      <c r="A48" s="15"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5" t="s">
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="5"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="4" t="s">
+      <c r="A49" s="15"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H49" s="5"/>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5" t="s">
+      <c r="A50" s="15"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H50" s="5"/>
+      <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="4" t="s">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H51" s="5"/>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5" t="s">
+      <c r="A52" s="15"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H52" s="5"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="4" t="s">
+      <c r="A53" s="15"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H53" s="5"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5" t="s">
+      <c r="A54" s="15"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H54" s="5"/>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="22"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="4" t="s">
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5" t="s">
+      <c r="A57" s="15"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="4" t="s">
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="17"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5" t="s">
+      <c r="A59" s="15"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="4" t="s">
+      <c r="C60" s="4"/>
+      <c r="D60" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
-      <c r="B61" s="5" t="s">
+      <c r="A61" s="15"/>
+      <c r="B61" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5" t="s">
+      <c r="C61" s="4"/>
+      <c r="D61" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="4" t="s">
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5" t="s">
+      <c r="A63" s="15"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="17"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="4" t="s">
+      <c r="A64" s="15"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5" t="s">
+      <c r="A65" s="15"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="4" t="s">
+      <c r="A66" s="15"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="17"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5" t="s">
+      <c r="A67" s="15"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="17"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="4" t="s">
+      <c r="A68" s="15"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5" t="s">
+      <c r="A69" s="15"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="4" t="s">
+      <c r="B70" s="4"/>
+      <c r="C70" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="4" t="s">
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5" t="s">
+      <c r="A71" s="15"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5" t="s">
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="17"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="4" t="s">
+      <c r="A72" s="15"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5" t="s">
+      <c r="A73" s="15"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="26"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D75" s="5"/>
-      <c r="E75" s="4" t="s">
+      <c r="D75" s="34"/>
+      <c r="E75" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="4" t="s">
+      <c r="G75" s="34"/>
+      <c r="H75" s="35" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
-      <c r="B76" s="5" t="s">
+      <c r="A76" s="36"/>
+      <c r="B76" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5" t="s">
+      <c r="D76" s="4"/>
+      <c r="E76" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5" t="s">
+      <c r="G76" s="4"/>
+      <c r="H76" s="37" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="17"/>
-      <c r="B77" s="4" t="s">
+      <c r="A77" s="36"/>
+      <c r="B77" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="4" t="s">
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="41" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
-      <c r="B78" s="5" t="s">
+      <c r="A78" s="36"/>
+      <c r="B78" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5" t="s">
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="37" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
-      <c r="B79" s="4" t="s">
+      <c r="A79" s="36"/>
+      <c r="B79" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="17"/>
-      <c r="B80" s="5" t="s">
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="37"/>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="38"/>
+      <c r="B80" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="40"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="17" t="s">
+      <c r="A81" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="4" t="s">
+      <c r="B81" s="34"/>
+      <c r="C81" s="34"/>
+      <c r="D81" s="34"/>
+      <c r="E81" s="34"/>
+      <c r="F81" s="34"/>
+      <c r="G81" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="H81" s="5"/>
+      <c r="H81" s="35"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="17"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5" t="s">
+      <c r="A82" s="36"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H82" s="5"/>
+      <c r="H82" s="37"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="17"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="4" t="s">
+      <c r="A83" s="36"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H83" s="5"/>
+      <c r="H83" s="37"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="17"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5" t="s">
+      <c r="A84" s="36"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="H84" s="5"/>
+      <c r="H84" s="37"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="17"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="4" t="s">
+      <c r="A85" s="36"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H85" s="5"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="17"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5" t="s">
+      <c r="H85" s="37"/>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="38"/>
+      <c r="B86" s="39"/>
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="H86" s="5"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
+      <c r="H86" s="40"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+      <c r="B87" s="30"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="32"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
+      <c r="B88" s="30"/>
+      <c r="C88" s="31"/>
+      <c r="D88" s="31"/>
+      <c r="E88" s="31"/>
+      <c r="F88" s="31"/>
+      <c r="G88" s="31"/>
+      <c r="H88" s="32"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="31"/>
+      <c r="D89" s="31"/>
+      <c r="E89" s="31"/>
+      <c r="F89" s="31"/>
+      <c r="G89" s="31"/>
+      <c r="H89" s="32"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B90" s="18"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="18"/>
-      <c r="E90" s="18"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
-      <c r="H90" s="18"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="27"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27"/>
+      <c r="G90" s="27"/>
+      <c r="H90" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="27">
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B87:H87"/>
     <mergeCell ref="A81:A86"/>
     <mergeCell ref="B90:H90"/>
     <mergeCell ref="A60:A61"/>
@@ -5895,513 +6229,513 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="11">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11">
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
         <v>0.160417</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="11">
-        <v>0</v>
-      </c>
-      <c r="C8" s="11">
-        <v>0</v>
-      </c>
-      <c r="D8" s="11">
-        <v>0</v>
-      </c>
-      <c r="E8" s="11">
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="11">
-        <v>0</v>
-      </c>
-      <c r="C9" s="11">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11">
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="11">
-        <v>0</v>
-      </c>
-      <c r="C10" s="11">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="11">
-        <v>0</v>
-      </c>
-      <c r="C11" s="11">
-        <v>0</v>
-      </c>
-      <c r="D11" s="11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11">
+      <c r="B11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="11">
-        <v>0</v>
-      </c>
-      <c r="C12" s="11">
-        <v>0</v>
-      </c>
-      <c r="D12" s="11">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11">
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="11">
-        <v>0</v>
-      </c>
-      <c r="C13" s="11">
-        <v>0</v>
-      </c>
-      <c r="D13" s="11">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11">
+      <c r="B13" s="9">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="11">
-        <v>0</v>
-      </c>
-      <c r="C14" s="11">
-        <v>0</v>
-      </c>
-      <c r="D14" s="11">
-        <v>0</v>
-      </c>
-      <c r="E14" s="11">
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="11">
-        <v>0</v>
-      </c>
-      <c r="C15" s="11">
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
         <v>0.125</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="9">
         <v>0.246528</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="11">
-        <v>0</v>
-      </c>
-      <c r="C16" s="11">
-        <v>0</v>
-      </c>
-      <c r="D16" s="11">
-        <v>0</v>
-      </c>
-      <c r="E16" s="11">
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="11">
-        <v>0</v>
-      </c>
-      <c r="C17" s="11">
-        <v>0</v>
-      </c>
-      <c r="D17" s="11">
-        <v>0</v>
-      </c>
-      <c r="E17" s="11">
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="11">
-        <v>0</v>
-      </c>
-      <c r="C18" s="11">
-        <v>0</v>
-      </c>
-      <c r="D18" s="11">
-        <v>0</v>
-      </c>
-      <c r="E18" s="11">
+      <c r="B18" s="9">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="11">
-        <v>0</v>
-      </c>
-      <c r="C19" s="11">
-        <v>0</v>
-      </c>
-      <c r="D19" s="11">
-        <v>0</v>
-      </c>
-      <c r="E19" s="11">
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="11">
-        <v>0</v>
-      </c>
-      <c r="C20" s="11">
-        <v>0</v>
-      </c>
-      <c r="D20" s="11">
-        <v>0</v>
-      </c>
-      <c r="E20" s="11">
+      <c r="B20" s="9">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="11">
-        <v>0</v>
-      </c>
-      <c r="C21" s="11">
-        <v>0</v>
-      </c>
-      <c r="D21" s="11">
-        <v>0</v>
-      </c>
-      <c r="E21" s="11">
+      <c r="B21" s="9">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="11">
-        <v>0</v>
-      </c>
-      <c r="C22" s="11">
-        <v>0</v>
-      </c>
-      <c r="D22" s="11">
-        <v>0</v>
-      </c>
-      <c r="E22" s="11">
+      <c r="B22" s="9">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="11">
-        <v>0</v>
-      </c>
-      <c r="C23" s="11">
-        <v>0</v>
-      </c>
-      <c r="D23" s="11">
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
         <v>0.16666700000000001</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="11">
-        <v>0</v>
-      </c>
-      <c r="C24" s="11">
-        <v>0</v>
-      </c>
-      <c r="D24" s="11">
-        <v>0</v>
-      </c>
-      <c r="E24" s="11">
+      <c r="B24" s="9">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="11">
-        <v>0</v>
-      </c>
-      <c r="C25" s="11">
+      <c r="B25" s="9">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
         <v>0.25</v>
       </c>
-      <c r="D25" s="11">
-        <v>0</v>
-      </c>
-      <c r="E25" s="11">
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="11">
-        <v>0</v>
-      </c>
-      <c r="C26" s="11">
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9">
         <v>0.125</v>
       </c>
-      <c r="D26" s="11">
-        <v>0</v>
-      </c>
-      <c r="E26" s="11">
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="11">
-        <v>0</v>
-      </c>
-      <c r="C27" s="11">
-        <v>0</v>
-      </c>
-      <c r="D27" s="11">
+      <c r="B27" s="9">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
         <v>0.25</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="11">
-        <v>0</v>
-      </c>
-      <c r="C28" s="11">
-        <v>0</v>
-      </c>
-      <c r="D28" s="11">
-        <v>0</v>
-      </c>
-      <c r="E28" s="11">
+      <c r="B28" s="9">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="11">
-        <v>0</v>
-      </c>
-      <c r="C29" s="11">
-        <v>0</v>
-      </c>
-      <c r="D29" s="11">
-        <v>0</v>
-      </c>
-      <c r="E29" s="11">
+      <c r="B29" s="9">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="11">
-        <v>0</v>
-      </c>
-      <c r="C30" s="11">
-        <v>0</v>
-      </c>
-      <c r="D30" s="11">
+      <c r="B30" s="9">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
         <v>0.23958399999999999</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="11">
-        <v>0</v>
-      </c>
-      <c r="C31" s="11">
-        <v>0</v>
-      </c>
-      <c r="D31" s="11">
-        <v>0</v>
-      </c>
-      <c r="E31" s="11">
+      <c r="B31" s="9">
+        <v>0</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="11">
-        <v>0</v>
-      </c>
-      <c r="C32" s="11">
-        <v>0</v>
-      </c>
-      <c r="D32" s="11">
-        <v>0</v>
-      </c>
-      <c r="E32" s="11">
+      <c r="B32" s="9">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="11">
-        <v>0</v>
-      </c>
-      <c r="C33" s="11">
-        <v>0</v>
-      </c>
-      <c r="D33" s="11">
-        <v>0</v>
-      </c>
-      <c r="E33" s="11">
+      <c r="B33" s="9">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="12">
-        <v>0</v>
-      </c>
-      <c r="C34" s="12">
+      <c r="B34" s="10">
+        <v>0</v>
+      </c>
+      <c r="C34" s="10">
         <v>0.5</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="10">
         <v>1.0625</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="10">
         <v>0</v>
       </c>
     </row>
@@ -6420,45 +6754,45 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="15"/>
+      <c r="B5" s="13"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -6640,13 +6974,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72CE2EAB-5166-41C9-B5AD-F8D09569EB74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB22551-1683-43B8-BB91-8D48A225D892}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8250314-268E-4598-8786-37CC1B89A8BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2148332F-4A08-4D4F-8E51-0EB7E2BEC56A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190A99B8-A65B-4E38-BB66-2C03938E92ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B10BEBB3-B7A3-454D-A1ED-9521E0F80FF2}"/>
 </file>
--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B07C84CE-2C88-4C58-AD22-CC8F8BB5F1FB}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0E0E0E-BDFD-43E1-B282-D04263320BDE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -843,64 +843,16 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -909,13 +861,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -934,6 +880,60 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -964,13 +964,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1008,13 +1008,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1052,13 +1052,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1096,13 +1096,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1140,13 +1140,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1184,13 +1184,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1228,13 +1228,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1272,13 +1272,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1316,13 +1316,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1360,13 +1360,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1404,13 +1404,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1448,13 +1448,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1492,13 +1492,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1536,13 +1536,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1580,13 +1580,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1624,13 +1624,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1668,13 +1668,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1712,13 +1712,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1756,13 +1756,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1800,13 +1800,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1844,13 +1844,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1888,13 +1888,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1932,13 +1932,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1976,13 +1976,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2020,13 +2020,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2064,13 +2064,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2108,13 +2108,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2152,13 +2152,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2196,13 +2196,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2240,13 +2240,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2284,13 +2284,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2328,13 +2328,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2372,13 +2372,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2416,13 +2416,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2460,13 +2460,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2504,13 +2504,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2548,13 +2548,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2592,13 +2592,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2636,13 +2636,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2680,13 +2680,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2724,13 +2724,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2768,13 +2768,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2812,13 +2812,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2856,13 +2856,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2900,13 +2900,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2944,13 +2944,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2988,13 +2988,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3032,13 +3032,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3076,13 +3076,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3120,13 +3120,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3164,13 +3164,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3208,13 +3208,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3252,13 +3252,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3296,13 +3296,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3340,13 +3340,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3384,13 +3384,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3428,13 +3428,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3472,13 +3472,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3516,13 +3516,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3560,13 +3560,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3604,13 +3604,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3648,13 +3648,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3692,13 +3692,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3736,13 +3736,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3780,13 +3780,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3824,13 +3824,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3868,13 +3868,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3912,13 +3912,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3956,13 +3956,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4000,13 +4000,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4044,13 +4044,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4088,13 +4088,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4132,13 +4132,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4176,13 +4176,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4220,13 +4220,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4264,13 +4264,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4308,13 +4308,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4352,13 +4352,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4396,13 +4396,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4440,13 +4440,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4484,13 +4484,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4893,686 +4893,686 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H90"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="32.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="H4" s="24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="34" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="35"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="37"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="36"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="37"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="37"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39" t="s">
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="38"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="40"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="H8" s="22"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34" t="s">
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="35"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39" t="s">
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="38"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39" t="s">
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="40"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="H10" s="22"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="35"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4" t="s">
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="37"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="37"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="20"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="37"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="37"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39" t="s">
+      <c r="H13" s="20"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="38"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="40"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29" t="s">
+      <c r="H14" s="22"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="32"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+      <c r="B15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34" t="s">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34" t="s">
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="38"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39" t="s">
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="38"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39" t="s">
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="39"/>
-      <c r="H16" s="40"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B18" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35" t="s">
+      <c r="G18" s="18"/>
+      <c r="H18" s="19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
-      <c r="B18" s="4" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="37"/>
+      <c r="B19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="37" t="s">
+      <c r="G19" s="4"/>
+      <c r="H19" s="20" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="36"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="3" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="37"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="37"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4" t="s">
+      <c r="G20" s="4"/>
+      <c r="H20" s="20"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="37"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="37"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="3" t="s">
+      <c r="G21" s="4"/>
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="37"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="37"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="38"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39" t="s">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="20"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="38"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="40"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="33" t="s">
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="35"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39" t="s">
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="38"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="40"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="33" t="s">
+      <c r="H25" s="22"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34" t="s">
+      <c r="C26" s="18"/>
+      <c r="D26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34" t="s">
+      <c r="E26" s="18"/>
+      <c r="F26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="35" t="s">
+      <c r="H26" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="4" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="37"/>
+      <c r="B27" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="37" t="s">
+      <c r="H27" s="20" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="3" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="37"/>
+      <c r="B28" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="3" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="3" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="H28" s="23" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="4" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="37"/>
+      <c r="B29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4" t="s">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H28" s="37" t="s">
+      <c r="H29" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="37"/>
-    </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="4" t="s">
-        <v>58</v>
+      <c r="D30" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="37"/>
+      <c r="G30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="20"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="3" t="s">
-        <v>19</v>
+      <c r="D31" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="37"/>
+      <c r="G31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="20"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="4" t="s">
-        <v>60</v>
+      <c r="D32" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="37"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="3" t="s">
-        <v>53</v>
+      <c r="D33" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="37"/>
+      <c r="H33" s="20"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="4" t="s">
-        <v>61</v>
+      <c r="D34" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="37"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="3" t="s">
-        <v>12</v>
+      <c r="D35" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
-      <c r="H35" s="37"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="38"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39" t="s">
+      <c r="H35" s="20"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="37"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="20"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="38"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="40"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="28" t="s">
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="15"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="A39" s="40"/>
+      <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>65</v>
-      </c>
+      <c r="D39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
-      <c r="B40" s="4" t="s">
-        <v>66</v>
+      <c r="A40" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>69</v>
+      <c r="D40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
-      <c r="B41" s="3" t="s">
-        <v>12</v>
+      <c r="A41" s="40"/>
+      <c r="B41" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F41" s="4"/>
+      <c r="D41" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="15"/>
-      <c r="B42" s="4" t="s">
-        <v>70</v>
+      <c r="A42" s="40"/>
+      <c r="B42" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="4" t="s">
-        <v>71</v>
+      <c r="E42" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
-      <c r="B43" s="3" t="s">
-        <v>65</v>
+      <c r="A43" s="40"/>
+      <c r="B43" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
-      <c r="B44" s="4" t="s">
-        <v>72</v>
+      <c r="A44" s="40"/>
+      <c r="B44" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -5582,9 +5582,9 @@
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
-      <c r="B45" s="3" t="s">
-        <v>33</v>
+      <c r="A45" s="40"/>
+      <c r="B45" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -5594,9 +5594,9 @@
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
-      <c r="B46" s="4" t="s">
-        <v>73</v>
+      <c r="A46" s="40"/>
+      <c r="B46" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -5606,197 +5606,195 @@
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B47" s="4"/>
+      <c r="A47" s="40"/>
+      <c r="B47" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
-      <c r="G47" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
+      <c r="A48" s="40" t="s">
+        <v>75</v>
+      </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="4" t="s">
-        <v>20</v>
+      <c r="D48" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
-      <c r="G48" s="4" t="s">
-        <v>21</v>
+      <c r="G48" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="40"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="D49" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="3" t="s">
-        <v>19</v>
+      <c r="G49" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
+      <c r="A50" s="40"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="4" t="s">
-        <v>16</v>
+      <c r="G50" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="15" t="s">
-        <v>76</v>
-      </c>
+      <c r="A51" s="40"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
-      <c r="G51" s="3" t="s">
-        <v>19</v>
+      <c r="G51" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="15"/>
+      <c r="A52" s="40" t="s">
+        <v>76</v>
+      </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="4" t="s">
-        <v>21</v>
+      <c r="G52" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="40"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="3" t="s">
-        <v>19</v>
+      <c r="G53" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="15"/>
+      <c r="A54" s="40"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="40"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B55" s="20"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="22"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
+      <c r="B56" s="33"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="35"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="4" t="s">
-        <v>16</v>
+      <c r="H57" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
-        <v>80</v>
-      </c>
+      <c r="A58" s="40"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="F58" s="4"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
+      <c r="H58" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="40" t="s">
+        <v>80</v>
+      </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="4" t="s">
-        <v>47</v>
+      <c r="F59" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="A60" s="40"/>
+      <c r="B60" s="4"/>
       <c r="C60" s="4"/>
-      <c r="D60" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="D60" s="4"/>
       <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
+      <c r="F60" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
-      <c r="B61" s="4" t="s">
-        <v>54</v>
+      <c r="A61" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C61" s="4"/>
-      <c r="D61" s="4" t="s">
-        <v>54</v>
+      <c r="D61" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -5804,422 +5802,437 @@
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B62" s="4"/>
+      <c r="A62" s="40"/>
+      <c r="B62" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
+      <c r="D62" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
-      <c r="H62" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="40" t="s">
+        <v>83</v>
+      </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
-      <c r="H63" s="4" t="s">
-        <v>84</v>
+      <c r="H63" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="15"/>
+      <c r="A64" s="40"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
-      <c r="H64" s="3" t="s">
-        <v>13</v>
+      <c r="H64" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="40"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="4" t="s">
-        <v>85</v>
+      <c r="H65" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="15"/>
+      <c r="A66" s="40"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
-      <c r="H66" s="3" t="s">
-        <v>12</v>
+      <c r="H66" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="40"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
-      <c r="H67" s="4" t="s">
-        <v>86</v>
+      <c r="H67" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="15"/>
+      <c r="A68" s="40"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
-      <c r="H68" s="3" t="s">
-        <v>13</v>
+      <c r="H68" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="40"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
-      <c r="H69" s="4" t="s">
-        <v>87</v>
+      <c r="H69" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="s">
-        <v>119</v>
-      </c>
+      <c r="A70" s="40"/>
       <c r="B70" s="4"/>
-      <c r="C70" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="18" t="s">
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="19" t="s">
-        <v>47</v>
+      <c r="F71" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="15"/>
+      <c r="A72" s="40"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="3" t="s">
-        <v>52</v>
+      <c r="C72" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="19"/>
+      <c r="F72" s="15" t="s">
+        <v>47</v>
+      </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="40"/>
       <c r="B73" s="4"/>
-      <c r="C73" s="4" t="s">
-        <v>54</v>
+      <c r="C73" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="19"/>
+      <c r="F73" s="15"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="23" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="40"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B74" s="24"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="26"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="33" t="s">
+      <c r="B75" s="30"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="32"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="B75" s="34" t="s">
+      <c r="B76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="34" t="s">
+      <c r="C76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D75" s="34"/>
-      <c r="E75" s="34" t="s">
+      <c r="D76" s="18"/>
+      <c r="E76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F75" s="34" t="s">
+      <c r="F76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="34"/>
-      <c r="H75" s="35" t="s">
+      <c r="G76" s="18"/>
+      <c r="H76" s="19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="36"/>
-      <c r="B76" s="4" t="s">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="37"/>
+      <c r="B77" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C77" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4" t="s">
+      <c r="D77" s="4"/>
+      <c r="E77" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F77" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G76" s="4"/>
-      <c r="H76" s="37" t="s">
+      <c r="G77" s="4"/>
+      <c r="H77" s="20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="36"/>
-      <c r="B77" s="3" t="s">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="37"/>
+      <c r="B78" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="41" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="36"/>
-      <c r="B78" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
-      <c r="H78" s="37" t="s">
-        <v>96</v>
+      <c r="H78" s="23" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="36"/>
-      <c r="B79" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>12</v>
+      <c r="A79" s="37"/>
+      <c r="B79" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
-      <c r="H79" s="37"/>
-    </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="38"/>
-      <c r="B80" s="39" t="s">
+      <c r="H79" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="37"/>
+      <c r="B80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="20"/>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="38"/>
+      <c r="B81" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C80" s="39" t="s">
+      <c r="C81" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
-      <c r="F80" s="39"/>
-      <c r="G80" s="39"/>
-      <c r="H80" s="40"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="33" t="s">
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="22"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="B81" s="34"/>
-      <c r="C81" s="34"/>
-      <c r="D81" s="34"/>
-      <c r="E81" s="34"/>
-      <c r="F81" s="34"/>
-      <c r="G81" s="34" t="s">
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H81" s="35"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="36"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H82" s="37"/>
+      <c r="H82" s="19"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="36"/>
+      <c r="A83" s="37"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
-      <c r="G83" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H83" s="37"/>
+      <c r="G83" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H83" s="20"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="36"/>
+      <c r="A84" s="37"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
-      <c r="G84" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H84" s="37"/>
+      <c r="G84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="20"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="36"/>
+      <c r="A85" s="37"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H85" s="20"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="37"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H85" s="37"/>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="38"/>
-      <c r="B86" s="39"/>
-      <c r="C86" s="39"/>
-      <c r="D86" s="39"/>
-      <c r="E86" s="39"/>
-      <c r="F86" s="39"/>
-      <c r="G86" s="39" t="s">
+      <c r="H86" s="20"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="38"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="H86" s="40"/>
-    </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="29" t="s">
+      <c r="H87" s="22"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B87" s="30"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="32"/>
-    </row>
-    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="29" t="s">
+      <c r="B88" s="27"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="29"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B88" s="30"/>
-      <c r="C88" s="31"/>
-      <c r="D88" s="31"/>
-      <c r="E88" s="31"/>
-      <c r="F88" s="31"/>
-      <c r="G88" s="31"/>
-      <c r="H88" s="32"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="29" t="s">
+      <c r="B89" s="27"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="28"/>
+      <c r="G89" s="28"/>
+      <c r="H89" s="29"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B89" s="30"/>
-      <c r="C89" s="31"/>
-      <c r="D89" s="31"/>
-      <c r="E89" s="31"/>
-      <c r="F89" s="31"/>
-      <c r="G89" s="31"/>
-      <c r="H89" s="32"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="27"/>
-      <c r="H90" s="27"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28"/>
+      <c r="H90" s="29"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="39"/>
+      <c r="G91" s="39"/>
+      <c r="H91" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B74:H74"/>
-    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A26:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="A82:A87"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A70"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B90:H90"/>
     <mergeCell ref="B89:H89"/>
     <mergeCell ref="B88:H88"/>
-    <mergeCell ref="B87:H87"/>
-    <mergeCell ref="A81:A86"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A69"/>
-    <mergeCell ref="A75:A80"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A25:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A46"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6234,20 +6247,20 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -6803,6 +6816,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F57AE488C1C9C348AE667C65EC1B6349" ma:contentTypeVersion="84" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7ffe0223de2040b214974ba9767dc658">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c298670-db79-47a5-968d-a4570c34317f" xmlns:ns3="17e8e7ea-beb0-4155-adc4-5bfa61f32508" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0b0806029c900830a7d915fa99f226c3" ns2:_="" ns3:_="">
     <xsd:import namespace="3c298670-db79-47a5-968d-a4570c34317f"/>
@@ -6953,15 +6975,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6974,13 +6987,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB22551-1683-43B8-BB91-8D48A225D892}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2148332F-4A08-4D4F-8E51-0EB7E2BEC56A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2148332F-4A08-4D4F-8E51-0EB7E2BEC56A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB22551-1683-43B8-BB91-8D48A225D892}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B10BEBB3-B7A3-454D-A1ED-9521E0F80FF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B10BEBB3-B7A3-454D-A1ED-9521E0F80FF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0E0E0E-BDFD-43E1-B282-D04263320BDE}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBAE6665-607D-4912-B989-70F1FF878585}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -497,36 +497,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="19">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -556,26 +532,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -586,43 +542,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -798,40 +717,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -843,97 +785,79 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4899,1306 +4823,1306 @@
   <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="32.140625" customWidth="1"/>
+    <col min="1" max="8" width="47.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="19"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="28"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="20"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="37"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3" t="s">
+      <c r="A7" s="28"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="20"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="38"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="22"/>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18" t="s">
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="19"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21" t="s">
+      <c r="A10" s="29"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21" t="s">
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="22"/>
+      <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="19"/>
+      <c r="H11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="3" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="20"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21" t="s">
+      <c r="A14" s="29"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="22"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18" t="s">
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="18"/>
-      <c r="H16" s="19"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21" t="s">
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19" t="s">
+      <c r="G18" s="15"/>
+      <c r="H18" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="37"/>
-      <c r="B19" s="4" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="20" t="s">
+      <c r="G19" s="3"/>
+      <c r="H19" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
+      <c r="A20" s="28"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="20"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="37"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4" t="s">
+      <c r="A21" s="28"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="20"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="3" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="20"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21" t="s">
+      <c r="A23" s="29"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="22"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="19"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="19"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="38"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21" t="s">
+      <c r="A25" s="29"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="22"/>
+      <c r="H25" s="19"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18" t="s">
+      <c r="C26" s="15"/>
+      <c r="D26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18" t="s">
+      <c r="E26" s="15"/>
+      <c r="F26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="37"/>
-      <c r="B27" s="4" t="s">
+      <c r="A27" s="28"/>
+      <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4" t="s">
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="20" t="s">
+      <c r="H27" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="37"/>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="28"/>
+      <c r="B28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="3" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="3"/>
+      <c r="F28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="H28" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="37"/>
-      <c r="B29" s="4" t="s">
+      <c r="A29" s="28"/>
+      <c r="B29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4" t="s">
+      <c r="E29" s="3"/>
+      <c r="F29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="H29" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="3" t="s">
+      <c r="A30" s="28"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="3" t="s">
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="20"/>
+      <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="37"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4" t="s">
+      <c r="A31" s="28"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4" t="s">
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H31" s="20"/>
+      <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="3" t="s">
+      <c r="A32" s="28"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="20"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="37"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4" t="s">
+      <c r="A33" s="28"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="20"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="3" t="s">
+      <c r="A34" s="28"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="20"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="37"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4" t="s">
+      <c r="A35" s="28"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="20"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="3" t="s">
+      <c r="A36" s="28"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="20"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="38"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21" t="s">
+      <c r="A37" s="34"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="22"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="41" t="s">
+      <c r="A38" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="40"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4" t="s">
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="29"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="19"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="3" t="s">
+      <c r="C40" s="15"/>
+      <c r="D40" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="40"/>
-      <c r="B41" s="4" t="s">
+      <c r="A41" s="28"/>
+      <c r="B41" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4" t="s">
+      <c r="C41" s="3"/>
+      <c r="D41" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="40"/>
-      <c r="B42" s="3" t="s">
+      <c r="A42" s="28"/>
+      <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="3" t="s">
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="40"/>
-      <c r="B43" s="4" t="s">
+      <c r="A43" s="28"/>
+      <c r="B43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4" t="s">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="40"/>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="40"/>
-      <c r="B45" s="4" t="s">
+      <c r="A45" s="28"/>
+      <c r="B45" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="40"/>
-      <c r="B46" s="3" t="s">
+      <c r="A46" s="28"/>
+      <c r="B46" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="40"/>
-      <c r="B47" s="4" t="s">
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="17"/>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="29"/>
+      <c r="B47" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="19"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="40" t="s">
+      <c r="A48" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="3" t="s">
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="3" t="s">
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H48" s="4"/>
+      <c r="H48" s="16"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="40"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4" t="s">
+      <c r="A49" s="28"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4" t="s">
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H49" s="4"/>
+      <c r="H49" s="17"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="40"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="3" t="s">
+      <c r="A50" s="28"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="40"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4" t="s">
+      <c r="H50" s="17"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="29"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H51" s="4"/>
+      <c r="H51" s="19"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="40" t="s">
+      <c r="A52" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="3" t="s">
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H52" s="4"/>
+      <c r="H52" s="16"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="40"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4" t="s">
+      <c r="A53" s="28"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H53" s="4"/>
+      <c r="H53" s="17"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="40"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="3" t="s">
+      <c r="A54" s="28"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="40"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4" t="s">
+      <c r="H54" s="17"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="29"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="H55" s="19"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="33"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="35"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="26"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="40" t="s">
+      <c r="A57" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="3" t="s">
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="40"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4" t="s">
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="29"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="40" t="s">
+      <c r="A59" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="3" t="s">
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="40"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4" t="s">
+      <c r="G59" s="15"/>
+      <c r="H59" s="16"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="29"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="19"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="40" t="s">
+      <c r="A61" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="3" t="s">
+      <c r="C61" s="15"/>
+      <c r="D61" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="40"/>
-      <c r="B62" s="4" t="s">
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="16"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="29"/>
+      <c r="B62" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4" t="s">
+      <c r="C62" s="18"/>
+      <c r="D62" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="19"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="3" t="s">
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="15"/>
+      <c r="H63" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="40"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4" t="s">
+      <c r="A64" s="28"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="17" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="40"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="3" t="s">
+      <c r="A65" s="28"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="40"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4" t="s">
+      <c r="A66" s="28"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="17" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="40"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="3" t="s">
+      <c r="A67" s="28"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="40"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4" t="s">
+      <c r="A68" s="28"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="17" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="40"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="3" t="s">
+      <c r="A69" s="28"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="40"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4" t="s">
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="34"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="17" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="40" t="s">
+      <c r="A71" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="3" t="s">
+      <c r="B71" s="15"/>
+      <c r="C71" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="14" t="s">
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="16"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="40"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4" t="s">
+      <c r="A72" s="28"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="15" t="s">
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="17"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="40"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="3" t="s">
+      <c r="A73" s="28"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="40"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4" t="s">
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="17"/>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="29"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="19"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B75" s="30"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="32"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="26"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="36" t="s">
+      <c r="A76" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="B76" s="18" t="s">
+      <c r="B76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C76" s="18" t="s">
+      <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18" t="s">
+      <c r="D76" s="3"/>
+      <c r="E76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F76" s="18" t="s">
+      <c r="F76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="18"/>
-      <c r="H76" s="19" t="s">
+      <c r="G76" s="3"/>
+      <c r="H76" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="37"/>
-      <c r="B77" s="4" t="s">
+      <c r="A77" s="28"/>
+      <c r="B77" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4" t="s">
+      <c r="D77" s="3"/>
+      <c r="E77" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G77" s="4"/>
-      <c r="H77" s="20" t="s">
+      <c r="G77" s="3"/>
+      <c r="H77" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="37"/>
-      <c r="B78" s="3" t="s">
+      <c r="A78" s="28"/>
+      <c r="B78" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="23" t="s">
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="37"/>
-      <c r="B79" s="4" t="s">
+      <c r="A79" s="28"/>
+      <c r="B79" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="20" t="s">
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="37"/>
-      <c r="B80" s="3" t="s">
+      <c r="A80" s="28"/>
+      <c r="B80" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="20"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="17"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="38"/>
-      <c r="B81" s="21" t="s">
+      <c r="A81" s="29"/>
+      <c r="B81" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="22"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="18"/>
+      <c r="H81" s="19"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="36" t="s">
+      <c r="A82" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="18" t="s">
+      <c r="B82" s="15"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="15"/>
+      <c r="G82" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H82" s="19"/>
+      <c r="H82" s="16"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="37"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4" t="s">
+      <c r="A83" s="28"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H83" s="20"/>
+      <c r="H83" s="17"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="37"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="3" t="s">
+      <c r="A84" s="28"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H84" s="20"/>
+      <c r="H84" s="17"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="37"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4" t="s">
+      <c r="A85" s="28"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H85" s="20"/>
+      <c r="H85" s="17"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="37"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="3" t="s">
+      <c r="A86" s="28"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H86" s="20"/>
+      <c r="H86" s="17"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="38"/>
-      <c r="B87" s="21"/>
-      <c r="C87" s="21"/>
-      <c r="D87" s="21"/>
-      <c r="E87" s="21"/>
-      <c r="F87" s="21"/>
-      <c r="G87" s="21" t="s">
+      <c r="A87" s="29"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="H87" s="22"/>
+      <c r="H87" s="19"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="17" t="s">
+      <c r="A88" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B88" s="27"/>
-      <c r="C88" s="28"/>
-      <c r="D88" s="28"/>
-      <c r="E88" s="28"/>
-      <c r="F88" s="28"/>
-      <c r="G88" s="28"/>
-      <c r="H88" s="29"/>
+      <c r="B88" s="24"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="26"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="17" t="s">
+      <c r="A89" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B89" s="27"/>
-      <c r="C89" s="28"/>
-      <c r="D89" s="28"/>
-      <c r="E89" s="28"/>
-      <c r="F89" s="28"/>
-      <c r="G89" s="28"/>
-      <c r="H89" s="29"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="H89" s="26"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="17" t="s">
+      <c r="A90" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B90" s="27"/>
-      <c r="C90" s="28"/>
-      <c r="D90" s="28"/>
-      <c r="E90" s="28"/>
-      <c r="F90" s="28"/>
-      <c r="G90" s="28"/>
-      <c r="H90" s="29"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B91" s="39"/>
-      <c r="C91" s="39"/>
-      <c r="D91" s="39"/>
-      <c r="E91" s="39"/>
-      <c r="F91" s="39"/>
-      <c r="G91" s="39"/>
-      <c r="H91" s="39"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="26"/>
+    </row>
+    <row r="91" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
+      <c r="G91" s="30"/>
+      <c r="H91" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -6231,7 +6155,7 @@
     <mergeCell ref="B88:H88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6242,513 +6166,513 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="9">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
         <v>0.160417</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="9">
-        <v>0</v>
-      </c>
-      <c r="C8" s="9">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="9">
-        <v>0</v>
-      </c>
-      <c r="C9" s="9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="B9" s="8">
+        <v>0</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="9">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="B10" s="8">
+        <v>0</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="9">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="B11" s="8">
+        <v>0</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="9">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9">
+      <c r="B12" s="8">
+        <v>0</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="9">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="B13" s="8">
+        <v>0</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="9">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="B14" s="8">
+        <v>0</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="9">
-        <v>0</v>
-      </c>
-      <c r="C15" s="9">
+      <c r="B15" s="8">
+        <v>0</v>
+      </c>
+      <c r="C15" s="8">
         <v>0.125</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>0.246528</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="9">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9">
+      <c r="B16" s="8">
+        <v>0</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="9">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9">
+      <c r="B17" s="8">
+        <v>0</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="9">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9">
-        <v>0</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9">
+      <c r="B18" s="8">
+        <v>0</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="9">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9">
-        <v>0</v>
-      </c>
-      <c r="D19" s="9">
-        <v>0</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="B19" s="8">
+        <v>0</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="9">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9">
-        <v>0</v>
-      </c>
-      <c r="D20" s="9">
-        <v>0</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="B20" s="8">
+        <v>0</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="9">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9">
-        <v>0</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="B21" s="8">
+        <v>0</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="9">
-        <v>0</v>
-      </c>
-      <c r="C22" s="9">
-        <v>0</v>
-      </c>
-      <c r="D22" s="9">
-        <v>0</v>
-      </c>
-      <c r="E22" s="9">
+      <c r="B22" s="8">
+        <v>0</v>
+      </c>
+      <c r="C22" s="8">
+        <v>0</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="9">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9">
-        <v>0</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="B23" s="8">
+        <v>0</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
         <v>0.16666700000000001</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="9">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9">
-        <v>0</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9">
+      <c r="B24" s="8">
+        <v>0</v>
+      </c>
+      <c r="C24" s="8">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="9">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9">
+      <c r="B25" s="8">
+        <v>0</v>
+      </c>
+      <c r="C25" s="8">
         <v>0.25</v>
       </c>
-      <c r="D25" s="9">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9">
+      <c r="D25" s="8">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="9">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9">
+      <c r="B26" s="8">
+        <v>0</v>
+      </c>
+      <c r="C26" s="8">
         <v>0.125</v>
       </c>
-      <c r="D26" s="9">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9">
+      <c r="D26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="9">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9">
+      <c r="B27" s="8">
+        <v>0</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
         <v>0.25</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="9">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9">
-        <v>0</v>
-      </c>
-      <c r="D28" s="9">
-        <v>0</v>
-      </c>
-      <c r="E28" s="9">
+      <c r="B28" s="8">
+        <v>0</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="9">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9">
-        <v>0</v>
-      </c>
-      <c r="D29" s="9">
-        <v>0</v>
-      </c>
-      <c r="E29" s="9">
+      <c r="B29" s="8">
+        <v>0</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="9">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9">
-        <v>0</v>
-      </c>
-      <c r="D30" s="9">
+      <c r="B30" s="8">
+        <v>0</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0</v>
+      </c>
+      <c r="D30" s="8">
         <v>0.23958399999999999</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="9">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9">
-        <v>0</v>
-      </c>
-      <c r="D31" s="9">
-        <v>0</v>
-      </c>
-      <c r="E31" s="9">
+      <c r="B31" s="8">
+        <v>0</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="9">
-        <v>0</v>
-      </c>
-      <c r="C32" s="9">
-        <v>0</v>
-      </c>
-      <c r="D32" s="9">
-        <v>0</v>
-      </c>
-      <c r="E32" s="9">
+      <c r="B32" s="8">
+        <v>0</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0</v>
+      </c>
+      <c r="D32" s="8">
+        <v>0</v>
+      </c>
+      <c r="E32" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="9">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9">
-        <v>0</v>
-      </c>
-      <c r="D33" s="9">
-        <v>0</v>
-      </c>
-      <c r="E33" s="9">
+      <c r="B33" s="8">
+        <v>0</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="10">
-        <v>0</v>
-      </c>
-      <c r="C34" s="10">
+      <c r="B34" s="9">
+        <v>0</v>
+      </c>
+      <c r="C34" s="9">
         <v>0.5</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>1.0625</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="9">
         <v>0</v>
       </c>
     </row>
@@ -6767,45 +6691,45 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="13"/>
+      <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>118</v>
       </c>
     </row>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBAE6665-607D-4912-B989-70F1FF878585}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4743E252-CE67-44E2-9459-37D9BC9D4E1B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -477,8 +477,14 @@
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,6 +499,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF66FF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -747,7 +771,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -860,6 +884,30 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -868,6 +916,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFCC"/>
+      <color rgb="FFCC99FF"/>
       <color rgb="FF66FF66"/>
     </mruColors>
   </colors>
@@ -5132,7 +5182,7 @@
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="42" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="2" t="s">
@@ -5150,7 +5200,7 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="28"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="43" t="s">
         <v>41</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -5259,7 +5309,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="28"/>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="38" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="3"/>
@@ -5279,7 +5329,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="39" t="s">
         <v>54</v>
       </c>
       <c r="C29" s="3"/>
@@ -5299,7 +5349,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
-      <c r="B30" s="3"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="3"/>
       <c r="D30" s="2" t="s">
         <v>53</v>
@@ -5313,7 +5363,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
-      <c r="B31" s="3"/>
+      <c r="B31" s="39"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
         <v>58</v>
@@ -5327,7 +5377,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="28"/>
-      <c r="B32" s="3"/>
+      <c r="B32" s="39"/>
       <c r="C32" s="3"/>
       <c r="D32" s="2" t="s">
         <v>19</v>
@@ -5339,7 +5389,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="28"/>
-      <c r="B33" s="3"/>
+      <c r="B33" s="39"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
         <v>60</v>
@@ -5351,7 +5401,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="28"/>
-      <c r="B34" s="3"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="3"/>
       <c r="D34" s="2" t="s">
         <v>53</v>
@@ -5363,7 +5413,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="28"/>
-      <c r="B35" s="3"/>
+      <c r="B35" s="39"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
         <v>61</v>
@@ -5375,7 +5425,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
-      <c r="B36" s="3"/>
+      <c r="B36" s="39"/>
       <c r="C36" s="3"/>
       <c r="D36" s="2" t="s">
         <v>12</v>
@@ -5387,7 +5437,7 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="34"/>
-      <c r="B37" s="3"/>
+      <c r="B37" s="39"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
         <v>62</v>
@@ -5431,7 +5481,7 @@
       <c r="A40" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="44" t="s">
         <v>33</v>
       </c>
       <c r="C40" s="15"/>
@@ -5449,7 +5499,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="28"/>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="45" t="s">
         <v>66</v>
       </c>
       <c r="C41" s="3"/>
@@ -5713,11 +5763,11 @@
       <c r="A61" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="40" t="s">
         <v>52</v>
       </c>
       <c r="C61" s="15"/>
-      <c r="D61" s="15" t="s">
+      <c r="D61" s="40" t="s">
         <v>52</v>
       </c>
       <c r="E61" s="15"/>
@@ -5727,11 +5777,11 @@
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="29"/>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="41" t="s">
         <v>54</v>
       </c>
       <c r="C62" s="18"/>
-      <c r="D62" s="18" t="s">
+      <c r="D62" s="41" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="18"/>
@@ -5870,7 +5920,7 @@
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="28"/>
       <c r="B73" s="3"/>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="38" t="s">
         <v>52</v>
       </c>
       <c r="D73" s="3"/>
@@ -5882,7 +5932,7 @@
     <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="29"/>
       <c r="B74" s="18"/>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="41" t="s">
         <v>54</v>
       </c>
       <c r="D74" s="18"/>
@@ -5947,10 +5997,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="28"/>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="42" t="s">
         <v>40</v>
       </c>
       <c r="D78" s="3"/>
@@ -5963,10 +6013,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="28"/>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="43" t="s">
         <v>95</v>
       </c>
       <c r="D79" s="3"/>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4743E252-CE67-44E2-9459-37D9BC9D4E1B}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0E0E0E-BDFD-43E1-B282-D04263320BDE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -477,14 +477,8 @@
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,31 +496,37 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC99FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="19">
+  <borders count="24">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -556,6 +556,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -566,6 +586,43 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -741,63 +798,40 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -809,103 +843,97 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -916,8 +944,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFCCFFCC"/>
-      <color rgb="FFCC99FF"/>
       <color rgb="FF66FF66"/>
     </mruColors>
   </colors>
@@ -4873,1306 +4899,1306 @@
   <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="47.28515625" customWidth="1"/>
+    <col min="1" max="8" width="32.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="16"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="37"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2" t="s">
+      <c r="A7" s="37"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="17"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18" t="s">
+      <c r="A8" s="38"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15" t="s">
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18" t="s">
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="16"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="37"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="17"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="2" t="s">
+      <c r="A13" s="37"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="17"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18" t="s">
+      <c r="A14" s="38"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="22"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15" t="s">
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18" t="s">
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16" t="s">
+      <c r="G18" s="18"/>
+      <c r="H18" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="37"/>
+      <c r="B19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="17" t="s">
+      <c r="G19" s="4"/>
+      <c r="H19" s="20" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="42" t="s">
+      <c r="A20" s="37"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="17"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="43" t="s">
+      <c r="A21" s="37"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="17"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="20"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="2" t="s">
+      <c r="A22" s="37"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="17"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18" t="s">
+      <c r="A23" s="38"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="16"/>
+      <c r="H24" s="19"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="29"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18" t="s">
+      <c r="A25" s="38"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="19"/>
+      <c r="H25" s="22"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15" t="s">
+      <c r="C26" s="18"/>
+      <c r="D26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15" t="s">
+      <c r="E26" s="18"/>
+      <c r="F26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="37"/>
+      <c r="B27" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
-      <c r="B28" s="38" t="s">
+      <c r="A28" s="37"/>
+      <c r="B28" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="2" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="39" t="s">
+      <c r="A29" s="37"/>
+      <c r="B29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3" t="s">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="20" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="28"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="2" t="s">
+      <c r="A30" s="37"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="2" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="17"/>
+      <c r="H30" s="20"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3" t="s">
+      <c r="A31" s="37"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3" t="s">
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H31" s="17"/>
+      <c r="H31" s="20"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="28"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="2" t="s">
+      <c r="A32" s="37"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="17"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3" t="s">
+      <c r="A33" s="37"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="17"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="20"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="2" t="s">
+      <c r="A34" s="37"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="17"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3" t="s">
+      <c r="A35" s="37"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="17"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="20"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="2" t="s">
+      <c r="A36" s="37"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="17"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="20"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3" t="s">
+      <c r="A37" s="38"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="17"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="29"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18" t="s">
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="40"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="19"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15" t="s">
+      <c r="C40" s="4"/>
+      <c r="D40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G40" s="15"/>
-      <c r="H40" s="16"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="45" t="s">
+      <c r="A41" s="40"/>
+      <c r="B41" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3" t="s">
+      <c r="C41" s="4"/>
+      <c r="D41" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="17"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
-      <c r="B42" s="2" t="s">
+      <c r="A42" s="40"/>
+      <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="2" t="s">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="17"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="3" t="s">
+      <c r="A43" s="40"/>
+      <c r="B43" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3" t="s">
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="17"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
-      <c r="B44" s="2" t="s">
+      <c r="A44" s="40"/>
+      <c r="B44" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="17"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="28"/>
-      <c r="B45" s="3" t="s">
+      <c r="A45" s="40"/>
+      <c r="B45" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="17"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="28"/>
-      <c r="B46" s="2" t="s">
+      <c r="A46" s="40"/>
+      <c r="B46" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="17"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="29"/>
-      <c r="B47" s="18" t="s">
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="40"/>
+      <c r="B47" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15" t="s">
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H48" s="16"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3" t="s">
+      <c r="A49" s="40"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3" t="s">
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H49" s="17"/>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="28"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="2" t="s">
+      <c r="A50" s="40"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H50" s="17"/>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="29"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18" t="s">
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="40"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H51" s="19"/>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15" t="s">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H52" s="16"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="28"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3" t="s">
+      <c r="A53" s="40"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H53" s="17"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="28"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="2" t="s">
+      <c r="A54" s="40"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H54" s="17"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="29"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18" t="s">
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="40"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H55" s="19"/>
-    </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14" t="s">
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="26"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="35"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="16" t="s">
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="29"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="19" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="40"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15" t="s">
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="15"/>
-      <c r="H59" s="16"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="29"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18" t="s">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="40"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G60" s="18"/>
-      <c r="H60" s="19"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="40" t="s">
+      <c r="B61" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="15"/>
-      <c r="D61" s="40" t="s">
+      <c r="C61" s="4"/>
+      <c r="D61" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="16"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="29"/>
-      <c r="B62" s="41" t="s">
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="40"/>
+      <c r="B62" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C62" s="18"/>
-      <c r="D62" s="41" t="s">
+      <c r="C62" s="4"/>
+      <c r="D62" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="19"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="16" t="s">
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="28"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="17" t="s">
+      <c r="A64" s="40"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="28"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="20" t="s">
+      <c r="A65" s="40"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="28"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="17" t="s">
+      <c r="A66" s="40"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="28"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="20" t="s">
+      <c r="A67" s="40"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="28"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="17" t="s">
+      <c r="A68" s="40"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="28"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="20" t="s">
+      <c r="A69" s="40"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="34"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="17" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="40"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15" t="s">
+      <c r="B71" s="4"/>
+      <c r="C71" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="36" t="s">
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G71" s="15"/>
-      <c r="H71" s="16"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="28"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3" t="s">
+      <c r="A72" s="40"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="13" t="s">
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="17"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="28"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="38" t="s">
+      <c r="A73" s="40"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="17"/>
-    </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="29"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="41" t="s">
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="40"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="19"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B75" s="24"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="26"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="32"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="35" t="s">
+      <c r="A76" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3" t="s">
+      <c r="D76" s="18"/>
+      <c r="E76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="17" t="s">
+      <c r="G76" s="18"/>
+      <c r="H76" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="28"/>
-      <c r="B77" s="3" t="s">
+      <c r="A77" s="37"/>
+      <c r="B77" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3" t="s">
+      <c r="D77" s="4"/>
+      <c r="E77" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="17" t="s">
+      <c r="G77" s="4"/>
+      <c r="H77" s="20" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="28"/>
-      <c r="B78" s="42" t="s">
+      <c r="A78" s="37"/>
+      <c r="B78" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="42" t="s">
+      <c r="C78" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="20" t="s">
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="28"/>
-      <c r="B79" s="43" t="s">
+      <c r="A79" s="37"/>
+      <c r="B79" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C79" s="43" t="s">
+      <c r="C79" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="17" t="s">
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="20" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="28"/>
-      <c r="B80" s="2" t="s">
+      <c r="A80" s="37"/>
+      <c r="B80" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="17"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="20"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="29"/>
-      <c r="B81" s="18" t="s">
+      <c r="A81" s="38"/>
+      <c r="B81" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-      <c r="H81" s="19"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="22"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="27" t="s">
+      <c r="A82" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15" t="s">
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H82" s="16"/>
+      <c r="H82" s="19"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="28"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
+      <c r="A83" s="37"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H83" s="17"/>
+      <c r="H83" s="20"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="28"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="2" t="s">
+      <c r="A84" s="37"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H84" s="17"/>
+      <c r="H84" s="20"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="28"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
+      <c r="A85" s="37"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="H85" s="17"/>
+      <c r="H85" s="20"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="28"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="2" t="s">
+      <c r="A86" s="37"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H86" s="17"/>
+      <c r="H86" s="20"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="29"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18" t="s">
+      <c r="A87" s="38"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="H87" s="19"/>
+      <c r="H87" s="22"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B88" s="24"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="26"/>
+      <c r="B88" s="27"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="29"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B89" s="24"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="25"/>
-      <c r="H89" s="26"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="28"/>
+      <c r="G89" s="28"/>
+      <c r="H89" s="29"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B90" s="24"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="25"/>
-      <c r="H90" s="26"/>
-    </row>
-    <row r="91" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
-      <c r="D91" s="30"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
-      <c r="H91" s="30"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28"/>
+      <c r="H90" s="29"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="39"/>
+      <c r="G91" s="39"/>
+      <c r="H91" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -6205,7 +6231,7 @@
     <mergeCell ref="B88:H88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6216,513 +6242,513 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="8">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
         <v>0.160417</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="8">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="8">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="8">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="B11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="8">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="8">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="B13" s="9">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="8">
-        <v>0</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="8">
-        <v>0</v>
-      </c>
-      <c r="C15" s="8">
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
         <v>0.125</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <v>0.246528</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="8">
-        <v>0</v>
-      </c>
-      <c r="C16" s="8">
-        <v>0</v>
-      </c>
-      <c r="D16" s="8">
-        <v>0</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="8">
-        <v>0</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
-        <v>0</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="8">
-        <v>0</v>
-      </c>
-      <c r="C18" s="8">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8">
-        <v>0</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="B18" s="9">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="8">
-        <v>0</v>
-      </c>
-      <c r="C19" s="8">
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8">
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="8">
-        <v>0</v>
-      </c>
-      <c r="C20" s="8">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8">
-        <v>0</v>
-      </c>
-      <c r="E20" s="8">
+      <c r="B20" s="9">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="8">
-        <v>0</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="B21" s="9">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="8">
-        <v>0</v>
-      </c>
-      <c r="C22" s="8">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="B22" s="9">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="8">
-        <v>0</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
         <v>0.16666700000000001</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="8">
-        <v>0</v>
-      </c>
-      <c r="C24" s="8">
-        <v>0</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8">
+      <c r="B24" s="9">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="8">
-        <v>0</v>
-      </c>
-      <c r="C25" s="8">
+      <c r="B25" s="9">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
         <v>0.25</v>
       </c>
-      <c r="D25" s="8">
-        <v>0</v>
-      </c>
-      <c r="E25" s="8">
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="8">
-        <v>0</v>
-      </c>
-      <c r="C26" s="8">
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9">
         <v>0.125</v>
       </c>
-      <c r="D26" s="8">
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="8">
-        <v>0</v>
-      </c>
-      <c r="C27" s="8">
-        <v>0</v>
-      </c>
-      <c r="D27" s="8">
+      <c r="B27" s="9">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
         <v>0.25</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="8">
-        <v>0</v>
-      </c>
-      <c r="C28" s="8">
-        <v>0</v>
-      </c>
-      <c r="D28" s="8">
-        <v>0</v>
-      </c>
-      <c r="E28" s="8">
+      <c r="B28" s="9">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="8">
-        <v>0</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0</v>
-      </c>
-      <c r="E29" s="8">
+      <c r="B29" s="9">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="8">
-        <v>0</v>
-      </c>
-      <c r="C30" s="8">
-        <v>0</v>
-      </c>
-      <c r="D30" s="8">
+      <c r="B30" s="9">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
         <v>0.23958399999999999</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="8">
-        <v>0</v>
-      </c>
-      <c r="C31" s="8">
-        <v>0</v>
-      </c>
-      <c r="D31" s="8">
-        <v>0</v>
-      </c>
-      <c r="E31" s="8">
+      <c r="B31" s="9">
+        <v>0</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="8">
-        <v>0</v>
-      </c>
-      <c r="C32" s="8">
-        <v>0</v>
-      </c>
-      <c r="D32" s="8">
-        <v>0</v>
-      </c>
-      <c r="E32" s="8">
+      <c r="B32" s="9">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="8">
-        <v>0</v>
-      </c>
-      <c r="C33" s="8">
-        <v>0</v>
-      </c>
-      <c r="D33" s="8">
-        <v>0</v>
-      </c>
-      <c r="E33" s="8">
+      <c r="B33" s="9">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="9">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9">
+      <c r="B34" s="10">
+        <v>0</v>
+      </c>
+      <c r="C34" s="10">
         <v>0.5</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="10">
         <v>1.0625</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <v>0</v>
       </c>
     </row>
@@ -6741,45 +6767,45 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="13"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>118</v>
       </c>
     </row>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4743E252-CE67-44E2-9459-37D9BC9D4E1B}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1631FF61-1CEF-4D11-B334-8DCF2FF97644}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -484,7 +484,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,6 +517,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -771,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -908,6 +914,18 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -916,6 +934,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFFF"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FFCC99FF"/>
       <color rgb="FF66FF66"/>
@@ -5313,7 +5332,7 @@
         <v>52</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="46" t="s">
         <v>19</v>
       </c>
       <c r="E28" s="3"/>
@@ -5333,7 +5352,7 @@
         <v>54</v>
       </c>
       <c r="C29" s="3"/>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="47" t="s">
         <v>55</v>
       </c>
       <c r="E29" s="3"/>
@@ -5351,7 +5370,7 @@
       <c r="A30" s="28"/>
       <c r="B30" s="39"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="46" t="s">
         <v>53</v>
       </c>
       <c r="E30" s="3"/>
@@ -5365,7 +5384,7 @@
       <c r="A31" s="28"/>
       <c r="B31" s="39"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="47" t="s">
         <v>58</v>
       </c>
       <c r="E31" s="3"/>
@@ -5379,7 +5398,7 @@
       <c r="A32" s="28"/>
       <c r="B32" s="39"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="46" t="s">
         <v>19</v>
       </c>
       <c r="E32" s="3"/>
@@ -5391,7 +5410,7 @@
       <c r="A33" s="28"/>
       <c r="B33" s="39"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="47" t="s">
         <v>60</v>
       </c>
       <c r="E33" s="3"/>
@@ -5403,7 +5422,7 @@
       <c r="A34" s="28"/>
       <c r="B34" s="39"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="46" t="s">
         <v>53</v>
       </c>
       <c r="E34" s="3"/>
@@ -5415,7 +5434,7 @@
       <c r="A35" s="28"/>
       <c r="B35" s="39"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="47" t="s">
         <v>61</v>
       </c>
       <c r="E35" s="3"/>
@@ -5569,7 +5588,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="28"/>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="46" t="s">
         <v>33</v>
       </c>
       <c r="C46" s="3"/>
@@ -5581,7 +5600,7 @@
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="29"/>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="49" t="s">
         <v>73</v>
       </c>
       <c r="C47" s="18"/>
@@ -5597,7 +5616,7 @@
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="48" t="s">
         <v>19</v>
       </c>
       <c r="E48" s="15"/>
@@ -5611,7 +5630,7 @@
       <c r="A49" s="28"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="47" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="3"/>
@@ -5625,7 +5644,7 @@
       <c r="A50" s="28"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="D50" s="47"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="2" t="s">
@@ -5637,7 +5656,7 @@
       <c r="A51" s="29"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
+      <c r="D51" s="49"/>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="18" t="s">

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1631FF61-1CEF-4D11-B334-8DCF2FF97644}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0E0E0E-BDFD-43E1-B282-D04263320BDE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -477,14 +477,8 @@
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,37 +496,37 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC99FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="19">
+  <borders count="24">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -562,6 +556,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -572,6 +586,43 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -747,63 +798,40 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -815,115 +843,97 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -934,9 +944,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFCCFFFF"/>
-      <color rgb="FFCCFFCC"/>
-      <color rgb="FFCC99FF"/>
       <color rgb="FF66FF66"/>
     </mruColors>
   </colors>
@@ -4892,1306 +4899,1306 @@
   <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="47.28515625" customWidth="1"/>
+    <col min="1" max="8" width="32.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="16"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="37"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2" t="s">
+      <c r="A7" s="37"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="17"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18" t="s">
+      <c r="A8" s="38"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15" t="s">
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18" t="s">
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="16"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="37"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="17"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="2" t="s">
+      <c r="A13" s="37"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="17"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18" t="s">
+      <c r="A14" s="38"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="22"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15" t="s">
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18" t="s">
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16" t="s">
+      <c r="G18" s="18"/>
+      <c r="H18" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="37"/>
+      <c r="B19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="17" t="s">
+      <c r="G19" s="4"/>
+      <c r="H19" s="20" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="42" t="s">
+      <c r="A20" s="37"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="17"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="43" t="s">
+      <c r="A21" s="37"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="17"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="20"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="2" t="s">
+      <c r="A22" s="37"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="17"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18" t="s">
+      <c r="A23" s="38"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="16"/>
+      <c r="H24" s="19"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="29"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18" t="s">
+      <c r="A25" s="38"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="19"/>
+      <c r="H25" s="22"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15" t="s">
+      <c r="C26" s="18"/>
+      <c r="D26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15" t="s">
+      <c r="E26" s="18"/>
+      <c r="F26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="37"/>
+      <c r="B27" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
-      <c r="B28" s="38" t="s">
+      <c r="A28" s="37"/>
+      <c r="B28" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="46" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="39" t="s">
+      <c r="A29" s="37"/>
+      <c r="B29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="47" t="s">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="20" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="28"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="46" t="s">
+      <c r="A30" s="37"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="2" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="17"/>
+      <c r="H30" s="20"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="47" t="s">
+      <c r="A31" s="37"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3" t="s">
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H31" s="17"/>
+      <c r="H31" s="20"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="28"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="46" t="s">
+      <c r="A32" s="37"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="17"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="47" t="s">
+      <c r="A33" s="37"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="17"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="20"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="46" t="s">
+      <c r="A34" s="37"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="17"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="47" t="s">
+      <c r="A35" s="37"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="17"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="20"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="2" t="s">
+      <c r="A36" s="37"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="17"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="20"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3" t="s">
+      <c r="A37" s="38"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="17"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="29"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18" t="s">
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="40"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="19"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15" t="s">
+      <c r="C40" s="4"/>
+      <c r="D40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G40" s="15"/>
-      <c r="H40" s="16"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="45" t="s">
+      <c r="A41" s="40"/>
+      <c r="B41" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3" t="s">
+      <c r="C41" s="4"/>
+      <c r="D41" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="17"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
-      <c r="B42" s="2" t="s">
+      <c r="A42" s="40"/>
+      <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="2" t="s">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="17"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="3" t="s">
+      <c r="A43" s="40"/>
+      <c r="B43" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3" t="s">
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="17"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
-      <c r="B44" s="2" t="s">
+      <c r="A44" s="40"/>
+      <c r="B44" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="17"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="28"/>
-      <c r="B45" s="3" t="s">
+      <c r="A45" s="40"/>
+      <c r="B45" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="17"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="28"/>
-      <c r="B46" s="46" t="s">
+      <c r="A46" s="40"/>
+      <c r="B46" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="17"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="29"/>
-      <c r="B47" s="49" t="s">
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="40"/>
+      <c r="B47" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="48" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15" t="s">
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H48" s="16"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="47" t="s">
+      <c r="A49" s="40"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3" t="s">
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H49" s="17"/>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="28"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="2" t="s">
+      <c r="A50" s="40"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H50" s="17"/>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="29"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18" t="s">
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="40"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H51" s="19"/>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15" t="s">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H52" s="16"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="28"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3" t="s">
+      <c r="A53" s="40"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H53" s="17"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="28"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="2" t="s">
+      <c r="A54" s="40"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H54" s="17"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="29"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18" t="s">
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="40"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H55" s="19"/>
-    </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14" t="s">
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="26"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="35"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="16" t="s">
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="29"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="19" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="40"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15" t="s">
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="15"/>
-      <c r="H59" s="16"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="29"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18" t="s">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="40"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G60" s="18"/>
-      <c r="H60" s="19"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B61" s="40" t="s">
+      <c r="B61" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="15"/>
-      <c r="D61" s="40" t="s">
+      <c r="C61" s="4"/>
+      <c r="D61" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="16"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="29"/>
-      <c r="B62" s="41" t="s">
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="40"/>
+      <c r="B62" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C62" s="18"/>
-      <c r="D62" s="41" t="s">
+      <c r="C62" s="4"/>
+      <c r="D62" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="19"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="16" t="s">
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="28"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="17" t="s">
+      <c r="A64" s="40"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="28"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="20" t="s">
+      <c r="A65" s="40"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="28"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="17" t="s">
+      <c r="A66" s="40"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="28"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="20" t="s">
+      <c r="A67" s="40"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="28"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="17" t="s">
+      <c r="A68" s="40"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="28"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="20" t="s">
+      <c r="A69" s="40"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="34"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="17" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="40"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15" t="s">
+      <c r="B71" s="4"/>
+      <c r="C71" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="36" t="s">
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G71" s="15"/>
-      <c r="H71" s="16"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="28"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3" t="s">
+      <c r="A72" s="40"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="13" t="s">
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="17"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="28"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="38" t="s">
+      <c r="A73" s="40"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="17"/>
-    </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="29"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="41" t="s">
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="40"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="19"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B75" s="24"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="26"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="32"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="35" t="s">
+      <c r="A76" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3" t="s">
+      <c r="D76" s="18"/>
+      <c r="E76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="17" t="s">
+      <c r="G76" s="18"/>
+      <c r="H76" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="28"/>
-      <c r="B77" s="3" t="s">
+      <c r="A77" s="37"/>
+      <c r="B77" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3" t="s">
+      <c r="D77" s="4"/>
+      <c r="E77" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="17" t="s">
+      <c r="G77" s="4"/>
+      <c r="H77" s="20" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="28"/>
-      <c r="B78" s="42" t="s">
+      <c r="A78" s="37"/>
+      <c r="B78" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="42" t="s">
+      <c r="C78" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="20" t="s">
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="28"/>
-      <c r="B79" s="43" t="s">
+      <c r="A79" s="37"/>
+      <c r="B79" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C79" s="43" t="s">
+      <c r="C79" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="17" t="s">
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="20" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="28"/>
-      <c r="B80" s="2" t="s">
+      <c r="A80" s="37"/>
+      <c r="B80" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="17"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="20"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="29"/>
-      <c r="B81" s="18" t="s">
+      <c r="A81" s="38"/>
+      <c r="B81" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-      <c r="H81" s="19"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="22"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="27" t="s">
+      <c r="A82" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15" t="s">
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H82" s="16"/>
+      <c r="H82" s="19"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="28"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
+      <c r="A83" s="37"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H83" s="17"/>
+      <c r="H83" s="20"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="28"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="2" t="s">
+      <c r="A84" s="37"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H84" s="17"/>
+      <c r="H84" s="20"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="28"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
+      <c r="A85" s="37"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="H85" s="17"/>
+      <c r="H85" s="20"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="28"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="2" t="s">
+      <c r="A86" s="37"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H86" s="17"/>
+      <c r="H86" s="20"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="29"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18" t="s">
+      <c r="A87" s="38"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="H87" s="19"/>
+      <c r="H87" s="22"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B88" s="24"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="26"/>
+      <c r="B88" s="27"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="29"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B89" s="24"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="25"/>
-      <c r="H89" s="26"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="28"/>
+      <c r="G89" s="28"/>
+      <c r="H89" s="29"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B90" s="24"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="25"/>
-      <c r="H90" s="26"/>
-    </row>
-    <row r="91" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
-      <c r="D91" s="30"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
-      <c r="H91" s="30"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28"/>
+      <c r="H90" s="29"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="39"/>
+      <c r="G91" s="39"/>
+      <c r="H91" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -6224,7 +6231,7 @@
     <mergeCell ref="B88:H88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6235,513 +6242,513 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="8">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
         <v>0.160417</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="8">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="8">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="8">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="B11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="8">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="8">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="B13" s="9">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="8">
-        <v>0</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="8">
-        <v>0</v>
-      </c>
-      <c r="C15" s="8">
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
         <v>0.125</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <v>0.246528</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="8">
-        <v>0</v>
-      </c>
-      <c r="C16" s="8">
-        <v>0</v>
-      </c>
-      <c r="D16" s="8">
-        <v>0</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="8">
-        <v>0</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
-        <v>0</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="8">
-        <v>0</v>
-      </c>
-      <c r="C18" s="8">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8">
-        <v>0</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="B18" s="9">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="8">
-        <v>0</v>
-      </c>
-      <c r="C19" s="8">
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8">
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="8">
-        <v>0</v>
-      </c>
-      <c r="C20" s="8">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8">
-        <v>0</v>
-      </c>
-      <c r="E20" s="8">
+      <c r="B20" s="9">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="8">
-        <v>0</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="B21" s="9">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="8">
-        <v>0</v>
-      </c>
-      <c r="C22" s="8">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="B22" s="9">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="8">
-        <v>0</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
         <v>0.16666700000000001</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="8">
-        <v>0</v>
-      </c>
-      <c r="C24" s="8">
-        <v>0</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8">
+      <c r="B24" s="9">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="8">
-        <v>0</v>
-      </c>
-      <c r="C25" s="8">
+      <c r="B25" s="9">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
         <v>0.25</v>
       </c>
-      <c r="D25" s="8">
-        <v>0</v>
-      </c>
-      <c r="E25" s="8">
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="8">
-        <v>0</v>
-      </c>
-      <c r="C26" s="8">
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9">
         <v>0.125</v>
       </c>
-      <c r="D26" s="8">
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="8">
-        <v>0</v>
-      </c>
-      <c r="C27" s="8">
-        <v>0</v>
-      </c>
-      <c r="D27" s="8">
+      <c r="B27" s="9">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
         <v>0.25</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="8">
-        <v>0</v>
-      </c>
-      <c r="C28" s="8">
-        <v>0</v>
-      </c>
-      <c r="D28" s="8">
-        <v>0</v>
-      </c>
-      <c r="E28" s="8">
+      <c r="B28" s="9">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="8">
-        <v>0</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0</v>
-      </c>
-      <c r="E29" s="8">
+      <c r="B29" s="9">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="8">
-        <v>0</v>
-      </c>
-      <c r="C30" s="8">
-        <v>0</v>
-      </c>
-      <c r="D30" s="8">
+      <c r="B30" s="9">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
         <v>0.23958399999999999</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="8">
-        <v>0</v>
-      </c>
-      <c r="C31" s="8">
-        <v>0</v>
-      </c>
-      <c r="D31" s="8">
-        <v>0</v>
-      </c>
-      <c r="E31" s="8">
+      <c r="B31" s="9">
+        <v>0</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="8">
-        <v>0</v>
-      </c>
-      <c r="C32" s="8">
-        <v>0</v>
-      </c>
-      <c r="D32" s="8">
-        <v>0</v>
-      </c>
-      <c r="E32" s="8">
+      <c r="B32" s="9">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="8">
-        <v>0</v>
-      </c>
-      <c r="C33" s="8">
-        <v>0</v>
-      </c>
-      <c r="D33" s="8">
-        <v>0</v>
-      </c>
-      <c r="E33" s="8">
+      <c r="B33" s="9">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="9">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9">
+      <c r="B34" s="10">
+        <v>0</v>
+      </c>
+      <c r="C34" s="10">
         <v>0.5</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="10">
         <v>1.0625</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <v>0</v>
       </c>
     </row>
@@ -6760,45 +6767,45 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="13"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>118</v>
       </c>
     </row>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1631FF61-1CEF-4D11-B334-8DCF2FF97644}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E844DFA-1BC6-4933-AC65-7C27292B49A7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="123">
   <si>
     <t>Planning des salariés du 12/10/2026 au 18/10/2026</t>
   </si>
@@ -225,9 +225,6 @@
     <t>10:15/11:45</t>
   </si>
   <si>
-    <t>14:15/21:00</t>
-  </si>
-  <si>
     <t>13:45/15:45</t>
   </si>
   <si>
@@ -237,9 +234,6 @@
     <t>11:45/12:15</t>
   </si>
   <si>
-    <t>16:30/22:30</t>
-  </si>
-  <si>
     <t>12:45/17:30</t>
   </si>
   <si>
@@ -382,6 +376,21 @@
   </si>
   <si>
     <t>PEREZ Loïc</t>
+  </si>
+  <si>
+    <t>14:15/15:30</t>
+  </si>
+  <si>
+    <t>15:30/16:30</t>
+  </si>
+  <si>
+    <t>16:30/17:30</t>
+  </si>
+  <si>
+    <t>16:30/21:00</t>
+  </si>
+  <si>
+    <t>17:30/22:30</t>
   </si>
 </sst>
 </file>
@@ -391,7 +400,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -483,8 +492,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -523,6 +538,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,7 +798,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -926,6 +947,30 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4508,6 +4553,270 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10715625" y="13335000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFEC9DA4-C35C-42FA-B81F-13B4CD25372A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="9915525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB8E2C9D-4014-43D4-83C9-AB87BE8CE45B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="10296525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9EC7EED-E0DB-4CF0-921D-A2F7338F2EB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="10677525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD60E20B-68FD-4820-A3F4-8B96FDE54C22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="9915525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{132D5ABE-CC67-4AC4-9012-FE4928199B68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="10296525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F59BED4-5CA3-4218-9E08-0B450C393476}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="10677525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5504,13 +5813,13 @@
         <v>33</v>
       </c>
       <c r="C40" s="15"/>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="57" t="s">
         <v>65</v>
       </c>
       <c r="G40" s="15"/>
@@ -5522,14 +5831,14 @@
         <v>66</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="55" t="s">
         <v>68</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="17"/>
@@ -5540,49 +5849,61 @@
         <v>12</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="2" t="s">
+      <c r="D42" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="E42" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="55"/>
       <c r="G42" s="3"/>
       <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="28"/>
       <c r="B43" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F43" s="3"/>
+      <c r="D43" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="55"/>
       <c r="G43" s="3"/>
       <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="28"/>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="54" t="s">
         <v>65</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+      <c r="D44" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="55"/>
       <c r="G44" s="3"/>
       <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="28"/>
-      <c r="B45" s="3" t="s">
-        <v>72</v>
+      <c r="B45" s="55" t="s">
+        <v>70</v>
       </c>
       <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
+      <c r="D45" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="F45" s="55"/>
       <c r="G45" s="3"/>
       <c r="H45" s="17"/>
     </row>
@@ -5592,27 +5913,27 @@
         <v>33</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="55"/>
       <c r="G46" s="3"/>
       <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="29"/>
       <c r="B47" s="49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="56"/>
       <c r="G47" s="18"/>
       <c r="H47" s="19"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -5666,7 +5987,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -5716,7 +6037,7 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
@@ -5728,7 +6049,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -5754,7 +6075,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -5780,7 +6101,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B61" s="40" t="s">
         <v>52</v>
@@ -5810,7 +6131,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -5831,7 +6152,7 @@
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -5855,7 +6176,7 @@
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -5879,7 +6200,7 @@
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -5903,12 +6224,12 @@
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15" t="s">
@@ -5962,7 +6283,7 @@
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
@@ -5974,7 +6295,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>12</v>
@@ -5991,23 +6312,23 @@
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="28"/>
       <c r="B77" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="17" t="s">
@@ -6033,17 +6354,17 @@
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="28"/>
       <c r="B79" s="43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C79" s="43" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -6063,7 +6384,7 @@
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="29"/>
       <c r="B81" s="18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>27</v>
@@ -6076,7 +6397,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -6096,7 +6417,7 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H83" s="17"/>
     </row>
@@ -6120,7 +6441,7 @@
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H85" s="17"/>
     </row>
@@ -6144,13 +6465,13 @@
       <c r="E87" s="18"/>
       <c r="F87" s="18"/>
       <c r="G87" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H87" s="19"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
@@ -6162,7 +6483,7 @@
     </row>
     <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
@@ -6174,7 +6495,7 @@
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
@@ -6241,7 +6562,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
@@ -6249,7 +6570,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="33" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
@@ -6260,16 +6581,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6461,7 +6782,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -6478,7 +6799,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B19" s="8">
         <v>0</v>
@@ -6495,7 +6816,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -6512,7 +6833,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -6529,7 +6850,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -6546,7 +6867,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B23" s="8">
         <v>0</v>
@@ -6563,7 +6884,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
@@ -6580,7 +6901,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
@@ -6597,7 +6918,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -6614,7 +6935,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
@@ -6631,7 +6952,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B28" s="8">
         <v>0</v>
@@ -6648,7 +6969,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B29" s="8">
         <v>0</v>
@@ -6665,7 +6986,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B30" s="8">
         <v>0</v>
@@ -6682,7 +7003,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B31" s="8">
         <v>0</v>
@@ -6699,7 +7020,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B32" s="8">
         <v>0</v>
@@ -6716,7 +7037,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B33" s="8">
         <v>0</v>
@@ -6766,40 +7087,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E844DFA-1BC6-4933-AC65-7C27292B49A7}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0E0E0E-BDFD-43E1-B282-D04263320BDE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="120">
   <si>
     <t>Planning des salariés du 12/10/2026 au 18/10/2026</t>
   </si>
@@ -225,6 +225,9 @@
     <t>10:15/11:45</t>
   </si>
   <si>
+    <t>14:15/21:00</t>
+  </si>
+  <si>
     <t>13:45/15:45</t>
   </si>
   <si>
@@ -234,6 +237,9 @@
     <t>11:45/12:15</t>
   </si>
   <si>
+    <t>16:30/22:30</t>
+  </si>
+  <si>
     <t>12:45/17:30</t>
   </si>
   <si>
@@ -376,21 +382,6 @@
   </si>
   <si>
     <t>PEREZ Loïc</t>
-  </si>
-  <si>
-    <t>14:15/15:30</t>
-  </si>
-  <si>
-    <t>15:30/16:30</t>
-  </si>
-  <si>
-    <t>16:30/17:30</t>
-  </si>
-  <si>
-    <t>16:30/21:00</t>
-  </si>
-  <si>
-    <t>17:30/22:30</t>
   </si>
 </sst>
 </file>
@@ -400,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -486,20 +477,8 @@
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,43 +496,37 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC99FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="19">
+  <borders count="24">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -583,6 +556,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -593,6 +586,43 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -768,63 +798,40 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -836,139 +843,97 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -979,9 +944,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFCCFFFF"/>
-      <color rgb="FFCCFFCC"/>
-      <color rgb="FFCC99FF"/>
       <color rgb="FF66FF66"/>
     </mruColors>
   </colors>
@@ -4553,270 +4515,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10715625" y="13335000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFEC9DA4-C35C-42FA-B81F-13B4CD25372A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="9915525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB8E2C9D-4014-43D4-83C9-AB87BE8CE45B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="10296525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9EC7EED-E0DB-4CF0-921D-A2F7338F2EB9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="10677525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD60E20B-68FD-4820-A3F4-8B96FDE54C22}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="9915525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{132D5ABE-CC67-4AC4-9012-FE4928199B68}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="10296525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F59BED4-5CA3-4218-9E08-0B450C393476}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="10677525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5201,1318 +4899,1306 @@
   <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="47.28515625" customWidth="1"/>
+    <col min="1" max="8" width="32.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="16"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="37"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2" t="s">
+      <c r="A7" s="37"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="17"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18" t="s">
+      <c r="A8" s="38"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15" t="s">
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18" t="s">
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="16"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="37"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="17"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="2" t="s">
+      <c r="A13" s="37"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="17"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18" t="s">
+      <c r="A14" s="38"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="22"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15" t="s">
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18" t="s">
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16" t="s">
+      <c r="G18" s="18"/>
+      <c r="H18" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="37"/>
+      <c r="B19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="17" t="s">
+      <c r="G19" s="4"/>
+      <c r="H19" s="20" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="42" t="s">
+      <c r="A20" s="37"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="17"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="43" t="s">
+      <c r="A21" s="37"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="17"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="20"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="2" t="s">
+      <c r="A22" s="37"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="17"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18" t="s">
+      <c r="A23" s="38"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="16"/>
+      <c r="H24" s="19"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="29"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18" t="s">
+      <c r="A25" s="38"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="19"/>
+      <c r="H25" s="22"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15" t="s">
+      <c r="C26" s="18"/>
+      <c r="D26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15" t="s">
+      <c r="E26" s="18"/>
+      <c r="F26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="37"/>
+      <c r="B27" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
-      <c r="B28" s="38" t="s">
+      <c r="A28" s="37"/>
+      <c r="B28" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="46" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="39" t="s">
+      <c r="A29" s="37"/>
+      <c r="B29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="47" t="s">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="20" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="28"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="46" t="s">
+      <c r="A30" s="37"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="2" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="17"/>
+      <c r="H30" s="20"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="47" t="s">
+      <c r="A31" s="37"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3" t="s">
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H31" s="17"/>
+      <c r="H31" s="20"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="28"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="46" t="s">
+      <c r="A32" s="37"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="17"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="47" t="s">
+      <c r="A33" s="37"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="17"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="20"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="46" t="s">
+      <c r="A34" s="37"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="17"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="47" t="s">
+      <c r="A35" s="37"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="17"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="20"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="2" t="s">
+      <c r="A36" s="37"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="17"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="20"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3" t="s">
+      <c r="A37" s="38"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="17"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="29"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18" t="s">
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="40"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="19"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="52" t="s">
+      <c r="C40" s="4"/>
+      <c r="D40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="52" t="s">
+      <c r="E40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="57" t="s">
+      <c r="F40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G40" s="15"/>
-      <c r="H40" s="16"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="45" t="s">
+      <c r="A41" s="40"/>
+      <c r="B41" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="53" t="s">
+      <c r="C41" s="4"/>
+      <c r="D41" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="55" t="s">
+      <c r="E41" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="17"/>
+      <c r="F41" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
-      <c r="B42" s="2" t="s">
+      <c r="A42" s="40"/>
+      <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="50" t="s">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="50" t="s">
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="40"/>
+      <c r="B43" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="40"/>
+      <c r="B44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="40"/>
+      <c r="B45" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="40"/>
+      <c r="B46" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="55"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="17"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="51" t="s">
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="40"/>
+      <c r="B47" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="40"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="40"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="40"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="40"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="40"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="40"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" s="33"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="35"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="40"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="40"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="40"/>
+      <c r="B62" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="40"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="40"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="40"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="40"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="40"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="40"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="40"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="55"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="17"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
-      <c r="B44" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="E44" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44" s="55"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="17"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="28"/>
-      <c r="B45" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="E45" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="55"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="17"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="28"/>
-      <c r="B46" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="17"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="29"/>
-      <c r="B47" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="48" t="s">
+      <c r="B71" s="4"/>
+      <c r="C71" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15" t="s">
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H48" s="16"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" s="17"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="28"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" s="17"/>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="29"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="H51" s="19"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" s="16"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="28"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" s="17"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="28"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H54" s="17"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="29"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="H55" s="19"/>
-    </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="26"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="16" t="s">
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="40"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="40"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="40"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" s="30"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="32"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" s="18"/>
+      <c r="H76" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="37"/>
+      <c r="B77" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G77" s="4"/>
+      <c r="H77" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="37"/>
+      <c r="B78" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="37"/>
+      <c r="B79" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="37"/>
+      <c r="B80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="20"/>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="38"/>
+      <c r="B81" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="22"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H82" s="19"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="37"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H83" s="20"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="37"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="29"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="15"/>
-      <c r="H59" s="16"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="29"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G60" s="18"/>
-      <c r="H60" s="19"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B61" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C61" s="15"/>
-      <c r="D61" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="16"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="29"/>
-      <c r="B62" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C62" s="18"/>
-      <c r="D62" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="19"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="16" t="s">
+      <c r="H84" s="20"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="37"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H85" s="20"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="37"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="28"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="28"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="28"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="28"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="28"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="28"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="34"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G71" s="15"/>
-      <c r="H71" s="16"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="28"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="17"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="28"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="17"/>
-    </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="29"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="19"/>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B75" s="24"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="26"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="28"/>
-      <c r="B77" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="28"/>
-      <c r="B78" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="28"/>
-      <c r="B79" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C79" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="28"/>
-      <c r="B80" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="17"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="29"/>
-      <c r="B81" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-      <c r="H81" s="19"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="H82" s="16"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="28"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H83" s="17"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="28"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H84" s="17"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="28"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H85" s="17"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="28"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H86" s="17"/>
+      <c r="H86" s="20"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="29"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="H87" s="19"/>
+      <c r="A87" s="38"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H87" s="22"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B88" s="24"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="26"/>
+      <c r="A88" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B88" s="27"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="29"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B89" s="24"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="25"/>
-      <c r="H89" s="26"/>
+      <c r="A89" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="27"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="28"/>
+      <c r="G89" s="28"/>
+      <c r="H89" s="29"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="B90" s="24"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="25"/>
-      <c r="H90" s="26"/>
-    </row>
-    <row r="91" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
-      <c r="D91" s="30"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
-      <c r="H91" s="30"/>
+      <c r="A90" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B90" s="27"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28"/>
+      <c r="H90" s="29"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="39"/>
+      <c r="G91" s="39"/>
+      <c r="H91" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -6545,7 +6231,7 @@
     <mergeCell ref="B88:H88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6556,513 +6242,513 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0.160417</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="9">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0.246528</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="9">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0.16666700000000001</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0.23958399999999999</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="33" t="s">
+      <c r="B32" s="9">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="8">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.160417</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="8">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="8">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="8">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="8">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="8">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="8">
-        <v>0</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="8">
-        <v>0</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.246528</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="8">
-        <v>0</v>
-      </c>
-      <c r="C16" s="8">
-        <v>0</v>
-      </c>
-      <c r="D16" s="8">
-        <v>0</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="8">
-        <v>0</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
-        <v>0</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="8">
-        <v>0</v>
-      </c>
-      <c r="C18" s="8">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8">
-        <v>0</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="8">
-        <v>0</v>
-      </c>
-      <c r="C19" s="8">
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="8">
-        <v>0</v>
-      </c>
-      <c r="C20" s="8">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8">
-        <v>0</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="8">
-        <v>0</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="8">
-        <v>0</v>
-      </c>
-      <c r="C22" s="8">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="8">
-        <v>0</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0.16666700000000001</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="8">
-        <v>0</v>
-      </c>
-      <c r="C24" s="8">
-        <v>0</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="8">
-        <v>0</v>
-      </c>
-      <c r="C25" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="D25" s="8">
-        <v>0</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="8">
-        <v>0</v>
-      </c>
-      <c r="C26" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="D26" s="8">
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="8">
-        <v>0</v>
-      </c>
-      <c r="C27" s="8">
-        <v>0</v>
-      </c>
-      <c r="D27" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="8">
-        <v>0</v>
-      </c>
-      <c r="C28" s="8">
-        <v>0</v>
-      </c>
-      <c r="D28" s="8">
-        <v>0</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="8">
-        <v>0</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="8">
-        <v>0</v>
-      </c>
-      <c r="C30" s="8">
-        <v>0</v>
-      </c>
-      <c r="D30" s="8">
-        <v>0.23958399999999999</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="8">
-        <v>0</v>
-      </c>
-      <c r="C31" s="8">
-        <v>0</v>
-      </c>
-      <c r="D31" s="8">
-        <v>0</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B32" s="8">
-        <v>0</v>
-      </c>
-      <c r="C32" s="8">
-        <v>0</v>
-      </c>
-      <c r="D32" s="8">
-        <v>0</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="8">
-        <v>0</v>
-      </c>
-      <c r="C33" s="8">
-        <v>0</v>
-      </c>
-      <c r="D33" s="8">
-        <v>0</v>
-      </c>
-      <c r="E33" s="8">
+      <c r="B33" s="9">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="9">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9">
+      <c r="B34" s="10">
+        <v>0</v>
+      </c>
+      <c r="C34" s="10">
         <v>0.5</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="10">
         <v>1.0625</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <v>0</v>
       </c>
     </row>
@@ -7081,46 +6767,46 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>110</v>
+      <c r="A4" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="12"/>
+      <c r="A5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="13"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>87</v>
+      <c r="A6" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>114</v>
+      <c r="A7" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>116</v>
+      <c r="A8" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5E9903F-BE8C-47BD-B9DD-B8D55647E601}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3507718D-17CE-4C39-A8CC-D54862028F0E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="126">
   <si>
     <t>Planning des salariés du 12/10/2026 au 18/10/2026</t>
   </si>
@@ -129,9 +129,6 @@
     <t>18:00/23:30</t>
   </si>
   <si>
-    <t>11:45/14:45</t>
-  </si>
-  <si>
     <t>10:00/12:30</t>
   </si>
   <si>
@@ -391,6 +388,18 @@
   </si>
   <si>
     <t>15:45/16:45</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>P25 // C. PADEL // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // P50F</t>
+  </si>
+  <si>
+    <t>EDF // ANNIV</t>
   </si>
 </sst>
 </file>
@@ -994,8 +1003,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFCC"/>
       <color rgb="FFCCFFFF"/>
-      <color rgb="FFCCFFCC"/>
       <color rgb="FFCC99FF"/>
       <color rgb="FF66FF66"/>
     </mruColors>
@@ -4904,6 +4913,138 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB07F81A-E79C-45A2-8525-E64E943B43EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15784286" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8E096D1-2E0E-48C1-AB91-7D570382017B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6313714" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A90214-FFC5-4AB9-A0A3-A71CF94FEEB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6313714" y="4082143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AFC12B0-6229-4577-8107-843617CFDFBF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5330,13 +5471,27 @@
       <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
@@ -5574,7 +5729,7 @@
       <c r="C18" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="41" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="41" t="s">
@@ -5593,30 +5748,30 @@
       <c r="B19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="42" t="s">
-        <v>37</v>
-      </c>
       <c r="F19" s="48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="27"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="C20" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="43" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -5631,17 +5786,17 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="27"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="F21" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="16"/>
@@ -5649,10 +5804,10 @@
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="27"/>
       <c r="B22" s="3"/>
-      <c r="C22" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="3"/>
+      <c r="C22" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="44"/>
       <c r="E22" s="3"/>
       <c r="F22" s="43" t="s">
         <v>33</v>
@@ -5663,13 +5818,13 @@
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="3"/>
-      <c r="C23" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="3"/>
+      <c r="C23" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="44"/>
       <c r="E23" s="3"/>
       <c r="F23" s="50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="16"/>
@@ -5677,8 +5832,10 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="33"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="44"/>
       <c r="E24" s="3"/>
       <c r="F24" s="62" t="s">
         <v>33</v>
@@ -5689,18 +5846,20 @@
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="28"/>
       <c r="B25" s="17"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="17"/>
+      <c r="C25" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="46"/>
       <c r="E25" s="17"/>
       <c r="F25" s="48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G25" s="17"/>
       <c r="H25" s="18"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -5726,7 +5885,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="45" t="s">
         <v>19</v>
@@ -5749,27 +5908,27 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="27"/>
       <c r="B29" s="44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="44" t="s">
+      <c r="H29" s="57" t="s">
         <v>48</v>
-      </c>
-      <c r="H29" s="57" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="27"/>
       <c r="B30" s="35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="43" t="s">
@@ -5780,7 +5939,7 @@
         <v>19</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H30" s="19" t="s">
         <v>12</v>
@@ -5789,21 +5948,21 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="27"/>
       <c r="B31" s="36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G31" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="16" t="s">
         <v>54</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -5811,7 +5970,7 @@
       <c r="B32" s="36"/>
       <c r="C32" s="3"/>
       <c r="D32" s="43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="44"/>
@@ -5825,12 +5984,12 @@
       <c r="B33" s="36"/>
       <c r="C33" s="3"/>
       <c r="D33" s="44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="44"/>
       <c r="G33" s="56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H33" s="16"/>
     </row>
@@ -5851,7 +6010,7 @@
       <c r="B35" s="36"/>
       <c r="C35" s="3"/>
       <c r="D35" s="44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="44"/>
@@ -5863,7 +6022,7 @@
       <c r="B36" s="36"/>
       <c r="C36" s="3"/>
       <c r="D36" s="43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="44"/>
@@ -5875,7 +6034,7 @@
       <c r="B37" s="36"/>
       <c r="C37" s="3"/>
       <c r="D37" s="44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="44"/>
@@ -5899,7 +6058,7 @@
       <c r="B39" s="36"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="44"/>
@@ -5908,7 +6067,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -5938,7 +6097,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" s="41" t="s">
         <v>33</v>
@@ -5951,7 +6110,7 @@
         <v>33</v>
       </c>
       <c r="F42" s="54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="15"/>
@@ -5959,17 +6118,17 @@
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="27"/>
       <c r="B43" s="42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E43" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" s="52" t="s">
         <v>65</v>
-      </c>
-      <c r="F43" s="52" t="s">
-        <v>66</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="16"/>
@@ -5993,14 +6152,14 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="27"/>
       <c r="B45" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45" s="48" t="s">
         <v>117</v>
-      </c>
-      <c r="E45" s="48" t="s">
-        <v>118</v>
       </c>
       <c r="F45" s="52"/>
       <c r="G45" s="3"/>
@@ -6009,7 +6168,7 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="27"/>
       <c r="B46" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="49" t="s">
@@ -6025,14 +6184,14 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="27"/>
       <c r="B47" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="50" t="s">
         <v>119</v>
-      </c>
-      <c r="E47" s="50" t="s">
-        <v>120</v>
       </c>
       <c r="F47" s="52"/>
       <c r="G47" s="3"/>
@@ -6053,7 +6212,7 @@
     <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="28"/>
       <c r="B49" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" s="17"/>
       <c r="D49" s="50"/>
@@ -6064,7 +6223,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -6118,7 +6277,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -6168,7 +6327,7 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B58" s="23"/>
       <c r="C58" s="24"/>
@@ -6180,7 +6339,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6206,7 +6365,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -6225,21 +6384,21 @@
       <c r="D62" s="17"/>
       <c r="E62" s="17"/>
       <c r="F62" s="46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G62" s="17"/>
       <c r="H62" s="18"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="14"/>
@@ -6249,11 +6408,11 @@
     <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="28"/>
       <c r="B64" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C64" s="17"/>
       <c r="D64" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
@@ -6262,7 +6421,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -6283,7 +6442,7 @@
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -6307,7 +6466,7 @@
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -6331,7 +6490,7 @@
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -6355,12 +6514,12 @@
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="45" t="s">
@@ -6378,12 +6537,12 @@
       <c r="A74" s="27"/>
       <c r="B74" s="3"/>
       <c r="C74" s="44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="16"/>
@@ -6392,7 +6551,7 @@
       <c r="A75" s="27"/>
       <c r="B75" s="3"/>
       <c r="C75" s="35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -6404,7 +6563,7 @@
       <c r="A76" s="28"/>
       <c r="B76" s="17"/>
       <c r="C76" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D76" s="17"/>
       <c r="E76" s="17"/>
@@ -6414,7 +6573,7 @@
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B77" s="23"/>
       <c r="C77" s="24"/>
@@ -6426,7 +6585,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>12</v>
@@ -6443,36 +6602,36 @@
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="27"/>
       <c r="B79" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="27"/>
       <c r="B80" s="39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -6485,17 +6644,17 @@
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="27"/>
       <c r="B81" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="40" t="s">
         <v>90</v>
-      </c>
-      <c r="C81" s="40" t="s">
-        <v>91</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -6515,7 +6674,7 @@
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="28"/>
       <c r="B83" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C83" s="17" t="s">
         <v>27</v>
@@ -6528,7 +6687,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -6548,7 +6707,7 @@
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H85" s="16"/>
     </row>
@@ -6572,7 +6731,7 @@
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H87" s="16"/>
     </row>
@@ -6596,13 +6755,13 @@
       <c r="E89" s="17"/>
       <c r="F89" s="17"/>
       <c r="G89" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H89" s="18"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B90" s="23"/>
       <c r="C90" s="24"/>
@@ -6614,7 +6773,7 @@
     </row>
     <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B91" s="23"/>
       <c r="C91" s="24"/>
@@ -6626,7 +6785,7 @@
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B92" s="23"/>
       <c r="C92" s="24"/>
@@ -6693,7 +6852,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
@@ -6701,7 +6860,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
@@ -6712,16 +6871,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6845,7 +7004,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="8">
         <v>0</v>
@@ -6862,7 +7021,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="8">
         <v>0</v>
@@ -6879,7 +7038,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="8">
         <v>0</v>
@@ -6896,7 +7055,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" s="8">
         <v>0</v>
@@ -6913,7 +7072,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -6930,7 +7089,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19" s="8">
         <v>0</v>
@@ -6947,7 +7106,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -6964,7 +7123,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -6981,7 +7140,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -6998,7 +7157,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="8">
         <v>0</v>
@@ -7015,7 +7174,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
@@ -7032,7 +7191,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
@@ -7049,7 +7208,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -7066,7 +7225,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
@@ -7083,7 +7242,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B28" s="8">
         <v>0</v>
@@ -7100,7 +7259,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B29" s="8">
         <v>0</v>
@@ -7117,7 +7276,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B30" s="8">
         <v>0</v>
@@ -7134,7 +7293,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B31" s="8">
         <v>0</v>
@@ -7151,7 +7310,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B32" s="8">
         <v>0</v>
@@ -7168,7 +7327,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B33" s="8">
         <v>0</v>
@@ -7218,40 +7377,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>107</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>111</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3507718D-17CE-4C39-A8CC-D54862028F0E}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4567FB6-8C46-4B3A-9C7E-D0B2DE2C5318}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="127">
   <si>
     <t>Planning des salariés du 12/10/2026 au 18/10/2026</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>EDF // ANNIV</t>
+  </si>
+  <si>
+    <t>18:30/24:00</t>
   </si>
 </sst>
 </file>
@@ -807,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -995,6 +998,9 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5061,6 +5067,50 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15784286" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7142A437-11A8-4543-A4ED-190545F00BE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6313714" y="2925536"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5693,7 +5743,9 @@
       <c r="A16" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="C16" s="14" t="s">
         <v>12</v>
       </c>
@@ -5707,7 +5759,9 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="63" t="s">
+        <v>126</v>
+      </c>
       <c r="C17" s="17" t="s">
         <v>15</v>
       </c>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4567FB6-8C46-4B3A-9C7E-D0B2DE2C5318}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B5B412B-8833-4E08-BB00-5193E17CAE45}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4550,23 +4550,551 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFEC9DA4-C35C-42FA-B81F-13B4CD25372A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="9915525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB8E2C9D-4014-43D4-83C9-AB87BE8CE45B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="10296525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9EC7EED-E0DB-4CF0-921D-A2F7338F2EB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="10677525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD60E20B-68FD-4820-A3F4-8B96FDE54C22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="9915525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{132D5ABE-CC67-4AC4-9012-FE4928199B68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="10296525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F59BED4-5CA3-4218-9E08-0B450C393476}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="10677525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A093A5F5-C2FB-4876-9832-C8B464CF1788}"/>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB61165D-7945-46DF-BBC4-5D6805634C4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15784286" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB07F81A-E79C-45A2-8525-E64E943B43EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15784286" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8E096D1-2E0E-48C1-AB91-7D570382017B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6313714" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A90214-FFC5-4AB9-A0A3-A71CF94FEEB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6313714" y="4082143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AFC12B0-6229-4577-8107-843617CFDFBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15784286" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7142A437-11A8-4543-A4ED-190545F00BE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6313714" y="2925536"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE4D76C7-93AD-4EF2-93EB-615117ABFD06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4582,535 +5110,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10715625" y="13335000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFEC9DA4-C35C-42FA-B81F-13B4CD25372A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="9915525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB8E2C9D-4014-43D4-83C9-AB87BE8CE45B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="10296525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9EC7EED-E0DB-4CF0-921D-A2F7338F2EB9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="10677525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD60E20B-68FD-4820-A3F4-8B96FDE54C22}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="9915525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{132D5ABE-CC67-4AC4-9012-FE4928199B68}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="10296525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F59BED4-5CA3-4218-9E08-0B450C393476}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="10677525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB61165D-7945-46DF-BBC4-5D6805634C4A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15784286" y="3701143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB07F81A-E79C-45A2-8525-E64E943B43EF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15784286" y="3701143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8E096D1-2E0E-48C1-AB91-7D570382017B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6313714" y="3701143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A90214-FFC5-4AB9-A0A3-A71CF94FEEB2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6313714" y="4082143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AFC12B0-6229-4577-8107-843617CFDFBF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15784286" y="3701143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7142A437-11A8-4543-A4ED-190545F00BE8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6313714" y="2925536"/>
+          <a:off x="15784286" y="11634107"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5641,7 +5641,9 @@
         <v>19</v>
       </c>
       <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="F9" s="45" t="s">
+        <v>19</v>
+      </c>
       <c r="G9" s="45" t="s">
         <v>19</v>
       </c>
@@ -5655,7 +5657,9 @@
         <v>20</v>
       </c>
       <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="F10" s="46" t="s">
+        <v>44</v>
+      </c>
       <c r="G10" s="46" t="s">
         <v>21</v>
       </c>
@@ -6581,9 +6585,7 @@
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
-      <c r="F73" s="45" t="s">
-        <v>19</v>
-      </c>
+      <c r="F73" s="14"/>
       <c r="G73" s="14"/>
       <c r="H73" s="15"/>
     </row>
@@ -6595,9 +6597,7 @@
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
-      <c r="F74" s="44" t="s">
-        <v>44</v>
-      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="16"/>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
-      <c r="F75" s="44"/>
+      <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="16"/>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D76" s="17"/>
       <c r="E76" s="17"/>
-      <c r="F76" s="46"/>
+      <c r="F76" s="17"/>
       <c r="G76" s="17"/>
       <c r="H76" s="18"/>
     </row>

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B5B412B-8833-4E08-BB00-5193E17CAE45}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C8F689-275D-4D83-A5EA-D25AB0510693}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6418,7 +6418,7 @@
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
       <c r="H60" s="60" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C8F689-275D-4D83-A5EA-D25AB0510693}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B5B412B-8833-4E08-BB00-5193E17CAE45}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6418,7 +6418,7 @@
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
       <c r="H60" s="60" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">

--- a/Plannings 2026 S42.xlsx
+++ b/Plannings 2026 S42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C8F689-275D-4D83-A5EA-D25AB0510693}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{77FDA8EE-4E4F-4FEB-9C0E-8650F5464317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B22952-A317-4CAE-BC28-84FE1C826DBF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="128">
   <si>
     <t>Planning des salariés du 12/10/2026 au 18/10/2026</t>
   </si>
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t>18:30/24:00</t>
+  </si>
+  <si>
+    <t>13:30/15:45</t>
   </si>
 </sst>
 </file>
@@ -810,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -950,6 +953,12 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1009,8 +1018,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFFF"/>
       <color rgb="FFCCFFCC"/>
-      <color rgb="FFCCFFFF"/>
       <color rgb="FFCC99FF"/>
       <color rgb="FF66FF66"/>
     </mruColors>
@@ -5111,6 +5120,182 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15784286" y="11634107"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC4835DD-2669-4EA4-95D2-7002638D1E90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="6867525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A07D484-6B62-4428-A9DD-C797D3748AA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="7248525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC6D62BC-5083-4867-A898-A1BF220CCC46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="7629525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E6E7BAA-26C0-40AD-AD68-B7723AC5BC20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="8010525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5584,7 +5769,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="14"/>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="63" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="15"/>
@@ -5602,7 +5787,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="56" t="s">
+      <c r="G6" s="58" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="16"/>
@@ -5763,7 +5948,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="65" t="s">
         <v>126</v>
       </c>
       <c r="C17" s="17" t="s">
@@ -5806,7 +5991,7 @@
       <c r="B19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="52" t="s">
         <v>40</v>
       </c>
       <c r="D19" s="42" t="s">
@@ -5815,7 +6000,7 @@
       <c r="E19" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="F19" s="50" t="s">
         <v>120</v>
       </c>
       <c r="G19" s="3"/>
@@ -5844,7 +6029,7 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="27"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="52" t="s">
         <v>64</v>
       </c>
       <c r="D21" s="44" t="s">
@@ -5853,7 +6038,7 @@
       <c r="E21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="52" t="s">
         <v>80</v>
       </c>
       <c r="G21" s="3"/>
@@ -5881,7 +6066,7 @@
       </c>
       <c r="D23" s="44"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="52" t="s">
         <v>64</v>
       </c>
       <c r="G23" s="3"/>
@@ -5895,7 +6080,7 @@
       </c>
       <c r="D24" s="44"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="62" t="s">
+      <c r="F24" s="64" t="s">
         <v>33</v>
       </c>
       <c r="G24" s="3"/>
@@ -5904,12 +6089,12 @@
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="28"/>
       <c r="B25" s="17"/>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="52" t="s">
         <v>41</v>
       </c>
       <c r="D25" s="46"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="48" t="s">
+      <c r="F25" s="50" t="s">
         <v>121</v>
       </c>
       <c r="G25" s="17"/>
@@ -5956,10 +6141,10 @@
       <c r="F28" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="45" t="s">
+      <c r="G28" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="59" t="s">
+      <c r="H28" s="61" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5976,10 +6161,10 @@
       <c r="F29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G29" s="44" t="s">
+      <c r="G29" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="H29" s="57" t="s">
+      <c r="H29" s="59" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5996,7 +6181,7 @@
       <c r="F30" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="43" t="s">
+      <c r="G30" s="51" t="s">
         <v>50</v>
       </c>
       <c r="H30" s="19" t="s">
@@ -6016,7 +6201,7 @@
       <c r="F31" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="G31" s="44" t="s">
+      <c r="G31" s="52" t="s">
         <v>53</v>
       </c>
       <c r="H31" s="16" t="s">
@@ -6032,8 +6217,8 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="44"/>
-      <c r="G32" s="55" t="s">
-        <v>13</v>
+      <c r="G32" s="47" t="s">
+        <v>12</v>
       </c>
       <c r="H32" s="16"/>
     </row>
@@ -6046,8 +6231,8 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="44"/>
-      <c r="G33" s="56" t="s">
-        <v>56</v>
+      <c r="G33" s="48" t="s">
+        <v>127</v>
       </c>
       <c r="H33" s="16"/>
     </row>
@@ -6060,7 +6245,9 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="44"/>
-      <c r="G34" s="56"/>
+      <c r="G34" s="57" t="s">
+        <v>13</v>
+      </c>
       <c r="H34" s="16"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -6072,7 +6259,9 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="44"/>
-      <c r="G35" s="56"/>
+      <c r="G35" s="58" t="s">
+        <v>48</v>
+      </c>
       <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -6084,7 +6273,7 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="44"/>
-      <c r="G36" s="56"/>
+      <c r="G36" s="58"/>
       <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -6096,7 +6285,7 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="44"/>
-      <c r="G37" s="56"/>
+      <c r="G37" s="58"/>
       <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -6108,7 +6297,7 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="44"/>
-      <c r="G38" s="56"/>
+      <c r="G38" s="58"/>
       <c r="H38" s="16"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6120,7 +6309,7 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="44"/>
-      <c r="G39" s="56"/>
+      <c r="G39" s="58"/>
       <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -6161,13 +6350,13 @@
         <v>33</v>
       </c>
       <c r="C42" s="14"/>
-      <c r="D42" s="49" t="s">
+      <c r="D42" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="49" t="s">
+      <c r="E42" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="54" t="s">
+      <c r="F42" s="56" t="s">
         <v>62</v>
       </c>
       <c r="G42" s="14"/>
@@ -6179,13 +6368,13 @@
         <v>63</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="50" t="s">
+      <c r="D43" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="E43" s="50" t="s">
+      <c r="E43" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="F43" s="52" t="s">
+      <c r="F43" s="54" t="s">
         <v>65</v>
       </c>
       <c r="G43" s="3"/>
@@ -6197,13 +6386,13 @@
         <v>12</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="47" t="s">
+      <c r="D44" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="E44" s="47" t="s">
+      <c r="E44" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="52"/>
+      <c r="F44" s="54"/>
       <c r="G44" s="3"/>
       <c r="H44" s="16"/>
     </row>
@@ -6213,45 +6402,45 @@
         <v>66</v>
       </c>
       <c r="C45" s="3"/>
-      <c r="D45" s="48" t="s">
+      <c r="D45" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="E45" s="48" t="s">
+      <c r="E45" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="F45" s="52"/>
+      <c r="F45" s="54"/>
       <c r="G45" s="3"/>
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="27"/>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="53" t="s">
         <v>62</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="49" t="s">
+      <c r="D46" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="49" t="s">
+      <c r="E46" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="F46" s="52"/>
+      <c r="F46" s="54"/>
       <c r="G46" s="3"/>
       <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="27"/>
-      <c r="B47" s="52" t="s">
+      <c r="B47" s="54" t="s">
         <v>67</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="50" t="s">
+      <c r="D47" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="E47" s="50" t="s">
+      <c r="E47" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="52"/>
+      <c r="F47" s="54"/>
       <c r="G47" s="3"/>
       <c r="H47" s="16"/>
     </row>
@@ -6261,9 +6450,9 @@
         <v>33</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="50"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="54"/>
       <c r="G48" s="3"/>
       <c r="H48" s="16"/>
     </row>
@@ -6273,9 +6462,9 @@
         <v>68</v>
       </c>
       <c r="C49" s="17"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="53"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="55"/>
       <c r="G49" s="17"/>
       <c r="H49" s="18"/>
     </row>
@@ -6405,7 +6594,7 @@
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
       <c r="G59" s="14"/>
-      <c r="H59" s="59" t="s">
+      <c r="H59" s="61" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6417,7 +6606,7 @@
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
-      <c r="H60" s="60" t="s">
+      <c r="H60" s="62" t="s">
         <v>56</v>
       </c>
     </row>
@@ -6511,7 +6700,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="58" t="s">
+      <c r="H67" s="60" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6523,7 +6712,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="57" t="s">
+      <c r="H68" s="59" t="s">
         <v>80</v>
       </c>
     </row>
@@ -6559,7 +6748,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="58" t="s">
+      <c r="H71" s="60" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6571,7 +6760,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="57" t="s">
+      <c r="H72" s="59" t="s">
         <v>82</v>
       </c>
     </row>
@@ -6655,7 +6844,7 @@
         <v>12</v>
       </c>
       <c r="G78" s="3"/>
-      <c r="H78" s="57" t="s">
+      <c r="H78" s="59" t="s">
         <v>85</v>
       </c>
     </row>
@@ -6675,7 +6864,7 @@
         <v>88</v>
       </c>
       <c r="G79" s="3"/>
-      <c r="H79" s="57" t="s">
+      <c r="H79" s="59" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6772,7 +6961,7 @@
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="55" t="s">
+      <c r="G86" s="57" t="s">
         <v>13</v>
       </c>
       <c r="H86" s="16"/>
@@ -6784,7 +6973,7 @@
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="56" t="s">
+      <c r="G87" s="58" t="s">
         <v>95</v>
       </c>
       <c r="H87" s="16"/>
